--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciano\Desktop\Distribuidora DAMAR\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciano\Downloads\app catalogo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -4622,7 +4622,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$ &quot;#,##0.00;\-&quot;$ &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4635,6 +4635,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
@@ -4695,7 +4702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4713,6 +4720,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5045,8 +5055,7 @@
         <v>558</v>
       </c>
       <c r="D3" s="6">
-        <f>VLOOKUP(A3,Hoja1!A:B,2,FALSE)</f>
-        <v>1011.11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5059,7 +5068,7 @@
       <c r="C4" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <f>VLOOKUP(A4,Hoja1!A:B,2,FALSE)</f>
         <v>2055.5100000000002</v>
       </c>
@@ -16536,6 +16545,7 @@
     <sortCondition ref="C2:C1225"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciano\Downloads\app catalogo\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciano\Desktop\Distribuidora DAMAR\2026\app catalogo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -5055,7 +5055,7 @@
         <v>558</v>
       </c>
       <c r="D3" s="6">
-        <v>1</v>
+        <v>1011.11</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -5654,7 +5654,10 @@
       <c r="C41" s="9" t="s">
         <v>1546</v>
       </c>
-      <c r="D41" s="6"/>
+      <c r="D41" s="6">
+        <f>VLOOKUP(A41,Hoja1!A:B,2,FALSE)</f>
+        <v>11396.6</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
@@ -5664,7 +5667,10 @@
       <c r="C42" s="9" t="s">
         <v>1547</v>
       </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="6">
+        <f>VLOOKUP(A42,Hoja1!A:B,2,FALSE)</f>
+        <v>11396.6</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
@@ -5674,7 +5680,10 @@
       <c r="C43" s="9" t="s">
         <v>1548</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="D43" s="6">
+        <f>VLOOKUP(A43,Hoja1!A:B,2,FALSE)</f>
+        <v>11396.6</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
@@ -5684,7 +5693,10 @@
       <c r="C44" s="9" t="s">
         <v>1549</v>
       </c>
-      <c r="D44" s="6"/>
+      <c r="D44" s="6">
+        <f>VLOOKUP(A44,Hoja1!A:B,2,FALSE)</f>
+        <v>4476.78</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
@@ -5694,7 +5706,10 @@
       <c r="C45" s="9" t="s">
         <v>1550</v>
       </c>
-      <c r="D45" s="6"/>
+      <c r="D45" s="6">
+        <f>VLOOKUP(A45,Hoja1!A:B,2,FALSE)</f>
+        <v>4476.78</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
@@ -5704,7 +5719,10 @@
       <c r="C46" s="9" t="s">
         <v>1551</v>
       </c>
-      <c r="D46" s="6"/>
+      <c r="D46" s="6">
+        <f>VLOOKUP(A46,Hoja1!A:B,2,FALSE)</f>
+        <v>3751.97</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
@@ -5714,7 +5732,10 @@
       <c r="C47" s="9" t="s">
         <v>1552</v>
       </c>
-      <c r="D47" s="6"/>
+      <c r="D47" s="6">
+        <f>VLOOKUP(A47,Hoja1!A:B,2,FALSE)</f>
+        <v>3751.97</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
@@ -5724,7 +5745,10 @@
       <c r="C48" s="9" t="s">
         <v>1553</v>
       </c>
-      <c r="D48" s="6"/>
+      <c r="D48" s="6">
+        <f>VLOOKUP(A48,Hoja1!A:B,2,FALSE)</f>
+        <v>4476.78</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
@@ -5734,7 +5758,10 @@
       <c r="C49" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="6">
+        <f>VLOOKUP(A49,Hoja1!A:B,2,FALSE)</f>
+        <v>1918.62</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
@@ -5744,7 +5771,10 @@
       <c r="C50" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D50" s="6"/>
+      <c r="D50" s="6">
+        <f>VLOOKUP(A50,Hoja1!A:B,2,FALSE)</f>
+        <v>1918.62</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
@@ -5754,7 +5784,10 @@
       <c r="C51" s="9" t="s">
         <v>1554</v>
       </c>
-      <c r="D51" s="6"/>
+      <c r="D51" s="6">
+        <f>VLOOKUP(A51,Hoja1!A:B,2,FALSE)</f>
+        <v>4476.78</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
@@ -5764,7 +5797,10 @@
       <c r="C52" s="9" t="s">
         <v>1555</v>
       </c>
-      <c r="D52" s="6"/>
+      <c r="D52" s="6">
+        <f>VLOOKUP(A52,Hoja1!A:B,2,FALSE)</f>
+        <v>3751.97</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
@@ -5774,7 +5810,10 @@
       <c r="C53" s="9" t="s">
         <v>1556</v>
       </c>
-      <c r="D53" s="6"/>
+      <c r="D53" s="6">
+        <f>VLOOKUP(A53,Hoja1!A:B,2,FALSE)</f>
+        <v>3751.97</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
@@ -5784,7 +5823,10 @@
       <c r="C54" s="9" t="s">
         <v>1557</v>
       </c>
-      <c r="D54" s="6"/>
+      <c r="D54" s="6">
+        <f>VLOOKUP(A54,Hoja1!A:B,2,FALSE)</f>
+        <v>3751.97</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -12967,4390 +12967,4390 @@
     </row>
     <row r="293" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
-        <v>10900</v>
-      </c>
-      <c r="B293" s="4" t="s">
-        <v>764</v>
-      </c>
+        <v>559115</v>
+      </c>
+      <c r="B293" s="4"/>
       <c r="C293" s="5" t="s">
-        <v>116</v>
+        <v>1432</v>
       </c>
       <c r="D293" s="6">
-        <f>VLOOKUP(A293,Hoja1!A:B,2,FALSE)</f>
-        <v>2839.49</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
-        <v>10412</v>
-      </c>
-      <c r="B294" s="4" t="s">
-        <v>742</v>
-      </c>
+        <v>559118</v>
+      </c>
+      <c r="B294" s="4"/>
       <c r="C294" s="5" t="s">
-        <v>117</v>
+        <v>1433</v>
       </c>
       <c r="D294" s="6">
-        <f>VLOOKUP(A294,Hoja1!A:B,2,FALSE)</f>
-        <v>6497.05</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
-        <v>10411</v>
-      </c>
-      <c r="B295" s="4" t="s">
-        <v>741</v>
-      </c>
+        <v>559117</v>
+      </c>
+      <c r="B295" s="4"/>
       <c r="C295" s="5" t="s">
-        <v>118</v>
+        <v>1434</v>
       </c>
       <c r="D295" s="6">
-        <f>VLOOKUP(A295,Hoja1!A:B,2,FALSE)</f>
-        <v>6497.05</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
-        <v>10400</v>
-      </c>
-      <c r="B296" s="4" t="s">
-        <v>762</v>
-      </c>
+        <v>559123</v>
+      </c>
+      <c r="B296" s="4"/>
       <c r="C296" s="5" t="s">
-        <v>119</v>
+        <v>1435</v>
       </c>
       <c r="D296" s="6">
-        <f>VLOOKUP(A296,Hoja1!A:B,2,FALSE)</f>
-        <v>3249.03</v>
+        <v>82767.839999999997</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
-        <v>10408</v>
-      </c>
-      <c r="B297" s="4" t="s">
-        <v>760</v>
-      </c>
+        <v>559120</v>
+      </c>
+      <c r="B297" s="4"/>
       <c r="C297" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D297" s="6" t="e">
-        <f>VLOOKUP(A297,Hoja1!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>1436</v>
+      </c>
+      <c r="D297" s="6">
+        <v>3448.66</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
-        <v>10403</v>
-      </c>
-      <c r="B298" s="4" t="s">
-        <v>779</v>
-      </c>
+        <v>559119</v>
+      </c>
+      <c r="B298" s="4"/>
       <c r="C298" s="5" t="s">
-        <v>121</v>
+        <v>1437</v>
       </c>
       <c r="D298" s="6">
-        <f>VLOOKUP(A298,Hoja1!A:B,2,FALSE)</f>
-        <v>3249.03</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
-        <v>10413</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>743</v>
-      </c>
+        <v>559121</v>
+      </c>
+      <c r="B299" s="4"/>
       <c r="C299" s="5" t="s">
-        <v>122</v>
+        <v>1438</v>
       </c>
       <c r="D299" s="6">
-        <f>VLOOKUP(A299,Hoja1!A:B,2,FALSE)</f>
-        <v>6497.05</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
-        <v>10402</v>
-      </c>
-      <c r="B300" s="4" t="s">
-        <v>763</v>
-      </c>
+        <v>559122</v>
+      </c>
+      <c r="B300" s="4"/>
       <c r="C300" s="5" t="s">
-        <v>123</v>
+        <v>1439</v>
       </c>
       <c r="D300" s="6">
-        <f>VLOOKUP(A300,Hoja1!A:B,2,FALSE)</f>
-        <v>3249.03</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
-        <v>10301</v>
-      </c>
-      <c r="B301" s="4" t="s">
-        <v>740</v>
-      </c>
+        <v>559116</v>
+      </c>
+      <c r="B301" s="4"/>
       <c r="C301" s="5" t="s">
-        <v>124</v>
+        <v>1440</v>
       </c>
       <c r="D301" s="6">
-        <f>VLOOKUP(A301,Hoja1!A:B,2,FALSE)</f>
-        <v>4022.61</v>
+        <v>3448.66</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
-        <v>10011</v>
+        <v>559114</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>772</v>
+        <v>963</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>125</v>
+        <v>519</v>
       </c>
       <c r="D302" s="6">
         <f>VLOOKUP(A302,Hoja1!A:B,2,FALSE)</f>
-        <v>8534.65</v>
+        <v>13310</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
-        <v>10012</v>
+        <v>559113</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>773</v>
+        <v>961</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>126</v>
+        <v>520</v>
       </c>
       <c r="D303" s="6">
         <f>VLOOKUP(A303,Hoja1!A:B,2,FALSE)</f>
-        <v>8534.65</v>
+        <v>13310</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
-        <v>10013</v>
+        <v>559107</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>774</v>
+        <v>962</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>127</v>
+        <v>521</v>
       </c>
       <c r="D304" s="6">
         <f>VLOOKUP(A304,Hoja1!A:B,2,FALSE)</f>
-        <v>8534.65</v>
+        <v>13310</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
-        <v>10206</v>
+        <v>10900</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D305" s="6">
         <f>VLOOKUP(A305,Hoja1!A:B,2,FALSE)</f>
-        <v>4734.5</v>
+        <v>2839.49</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
-        <v>10207</v>
+        <v>10412</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D306" s="6">
         <f>VLOOKUP(A306,Hoja1!A:B,2,FALSE)</f>
-        <v>4734.5</v>
+        <v>6497.05</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
-        <v>10205</v>
+        <v>10411</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D307" s="6">
         <f>VLOOKUP(A307,Hoja1!A:B,2,FALSE)</f>
-        <v>4734.5</v>
+        <v>6497.05</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
-        <v>10215</v>
+        <v>10400</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D308" s="6">
         <f>VLOOKUP(A308,Hoja1!A:B,2,FALSE)</f>
-        <v>7742.87</v>
+        <v>3249.03</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
-        <v>10216</v>
+        <v>10408</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D309" s="6">
+        <v>120</v>
+      </c>
+      <c r="D309" s="6" t="e">
         <f>VLOOKUP(A309,Hoja1!A:B,2,FALSE)</f>
-        <v>7742.87</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
-        <v>10217</v>
+        <v>10403</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>755</v>
+        <v>779</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D310" s="6">
         <f>VLOOKUP(A310,Hoja1!A:B,2,FALSE)</f>
-        <v>7742.87</v>
+        <v>3249.03</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
-        <v>10501</v>
+        <v>10413</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D311" s="6">
         <f>VLOOKUP(A311,Hoja1!A:B,2,FALSE)</f>
-        <v>6883.34</v>
+        <v>6497.05</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
-        <v>1043004</v>
+        <v>10402</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>222</v>
+        <v>123</v>
       </c>
       <c r="D312" s="6">
         <f>VLOOKUP(A312,Hoja1!A:B,2,FALSE)</f>
-        <v>1337.84</v>
+        <v>3249.03</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
-        <v>1047004</v>
+        <v>10301</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>793</v>
+        <v>740</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="D313" s="6">
         <f>VLOOKUP(A313,Hoja1!A:B,2,FALSE)</f>
-        <v>2601.85</v>
+        <v>4022.61</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
-        <v>1043001</v>
+        <v>10011</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="D314" s="6">
         <f>VLOOKUP(A314,Hoja1!A:B,2,FALSE)</f>
-        <v>1981.98</v>
+        <v>8534.65</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
-        <v>1047001</v>
+        <v>10012</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>794</v>
+        <v>773</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>225</v>
+        <v>126</v>
       </c>
       <c r="D315" s="6">
         <f>VLOOKUP(A315,Hoja1!A:B,2,FALSE)</f>
-        <v>2601.85</v>
+        <v>8534.65</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
-        <v>7220</v>
+        <v>10013</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1330</v>
+        <v>774</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="D316" s="6">
         <f>VLOOKUP(A316,Hoja1!A:B,2,FALSE)</f>
-        <v>2193.36</v>
+        <v>8534.65</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
-        <v>10088</v>
+        <v>10206</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>796</v>
+        <v>757</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D317" s="6">
         <f>VLOOKUP(A317,Hoja1!A:B,2,FALSE)</f>
-        <v>2304.56</v>
+        <v>4734.5</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
-        <v>10087</v>
+        <v>10207</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>795</v>
+        <v>758</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D318" s="6">
         <f>VLOOKUP(A318,Hoja1!A:B,2,FALSE)</f>
-        <v>2304.56</v>
+        <v>4734.5</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
-        <v>10086</v>
+        <v>10205</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>790</v>
+        <v>756</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D319" s="6">
         <f>VLOOKUP(A319,Hoja1!A:B,2,FALSE)</f>
-        <v>2304.56</v>
+        <v>4734.5</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
-        <v>16200</v>
+        <v>10215</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>781</v>
+        <v>753</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D320" s="6">
         <f>VLOOKUP(A320,Hoja1!A:B,2,FALSE)</f>
-        <v>3328.92</v>
+        <v>7742.87</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
-        <v>16205</v>
+        <v>10216</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>782</v>
+        <v>754</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D321" s="6">
         <f>VLOOKUP(A321,Hoja1!A:B,2,FALSE)</f>
-        <v>4053.96</v>
+        <v>7742.87</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
-        <v>16084</v>
+        <v>10217</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>778</v>
+        <v>755</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D322" s="6">
         <f>VLOOKUP(A322,Hoja1!A:B,2,FALSE)</f>
-        <v>1408.62</v>
+        <v>7742.87</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
-        <v>16077</v>
+        <v>10501</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>784</v>
+        <v>761</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D323" s="6">
         <f>VLOOKUP(A323,Hoja1!A:B,2,FALSE)</f>
-        <v>1408.62</v>
+        <v>6883.34</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
-        <v>16080</v>
+        <v>1043004</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>759</v>
+        <v>791</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
       <c r="D324" s="6">
         <f>VLOOKUP(A324,Hoja1!A:B,2,FALSE)</f>
-        <v>1408.62</v>
+        <v>1337.84</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
-        <v>16083</v>
+        <v>1047004</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D325" s="6" t="e">
+        <v>223</v>
+      </c>
+      <c r="D325" s="6">
         <f>VLOOKUP(A325,Hoja1!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>2601.85</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
-        <v>16081</v>
+        <v>1043001</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>775</v>
+        <v>792</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="D326" s="6">
         <f>VLOOKUP(A326,Hoja1!A:B,2,FALSE)</f>
-        <v>1408.62</v>
+        <v>1981.98</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
-        <v>16082</v>
+        <v>1047001</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>776</v>
+        <v>794</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="D327" s="6">
         <f>VLOOKUP(A327,Hoja1!A:B,2,FALSE)</f>
-        <v>1408.62</v>
+        <v>2601.85</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
-        <v>10509</v>
+        <v>7220</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>752</v>
+        <v>1330</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="D328" s="6">
         <f>VLOOKUP(A328,Hoja1!A:B,2,FALSE)</f>
-        <v>3478.58</v>
+        <v>2193.36</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
-        <v>16078</v>
+        <v>10088</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D329" s="6" t="e">
+        <v>135</v>
+      </c>
+      <c r="D329" s="6">
         <f>VLOOKUP(A329,Hoja1!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>2304.56</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
-        <v>10500</v>
+        <v>10087</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D330" s="6">
         <f>VLOOKUP(A330,Hoja1!A:B,2,FALSE)</f>
-        <v>2122.54</v>
+        <v>2304.56</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
-        <v>10516</v>
+        <v>10086</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D331" s="6">
         <f>VLOOKUP(A331,Hoja1!A:B,2,FALSE)</f>
-        <v>3478.58</v>
+        <v>2304.56</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
-        <v>10507</v>
+        <v>16200</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D332" s="6">
         <f>VLOOKUP(A332,Hoja1!A:B,2,FALSE)</f>
-        <v>3478.58</v>
+        <v>3328.92</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
-        <v>10511</v>
+        <v>16205</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D333" s="6">
         <f>VLOOKUP(A333,Hoja1!A:B,2,FALSE)</f>
-        <v>4394.74</v>
+        <v>4053.96</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
-        <v>10510</v>
+        <v>16084</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D334" s="6">
         <f>VLOOKUP(A334,Hoja1!A:B,2,FALSE)</f>
-        <v>7414.22</v>
+        <v>1408.62</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
-        <v>10508</v>
+        <v>16077</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D335" s="6">
         <f>VLOOKUP(A335,Hoja1!A:B,2,FALSE)</f>
-        <v>3478.58</v>
+        <v>1408.62</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
-        <v>10601</v>
+        <v>16080</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>745</v>
+        <v>759</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D336" s="6">
         <f>VLOOKUP(A336,Hoja1!A:B,2,FALSE)</f>
-        <v>3683.85</v>
+        <v>1408.62</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
-        <v>10609</v>
+        <v>16083</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D337" s="6">
+        <v>143</v>
+      </c>
+      <c r="D337" s="6" t="e">
         <f>VLOOKUP(A337,Hoja1!A:B,2,FALSE)</f>
-        <v>3350.15</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
-        <v>10605</v>
+        <v>16081</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>746</v>
+        <v>775</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D338" s="6">
         <f>VLOOKUP(A338,Hoja1!A:B,2,FALSE)</f>
-        <v>3683.85</v>
+        <v>1408.62</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
-        <v>10607</v>
+        <v>16082</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D339" s="6">
         <f>VLOOKUP(A339,Hoja1!A:B,2,FALSE)</f>
-        <v>3683.85</v>
+        <v>1408.62</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
-        <v>7224</v>
+        <v>10509</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1334</v>
+        <v>752</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D340" s="6">
         <f>VLOOKUP(A340,Hoja1!A:B,2,FALSE)</f>
-        <v>2778.04</v>
+        <v>3478.58</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
-        <v>7221</v>
+        <v>16078</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1331</v>
+        <v>783</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D341" s="6">
+        <v>147</v>
+      </c>
+      <c r="D341" s="6" t="e">
         <f>VLOOKUP(A341,Hoja1!A:B,2,FALSE)</f>
-        <v>2699.88</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
-        <v>7227</v>
+        <v>10500</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1337</v>
+        <v>765</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D342" s="6">
         <f>VLOOKUP(A342,Hoja1!A:B,2,FALSE)</f>
-        <v>2416.91</v>
+        <v>2122.54</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
-        <v>7223</v>
+        <v>10516</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1333</v>
+        <v>744</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D343" s="6">
         <f>VLOOKUP(A343,Hoja1!A:B,2,FALSE)</f>
-        <v>2276.21</v>
+        <v>3478.58</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
-        <v>7222</v>
+        <v>10507</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1332</v>
+        <v>787</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D344" s="6">
         <f>VLOOKUP(A344,Hoja1!A:B,2,FALSE)</f>
-        <v>2193.36</v>
+        <v>3478.58</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
-        <v>10702</v>
+        <v>10511</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>739</v>
+        <v>788</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D345" s="6">
         <f>VLOOKUP(A345,Hoja1!A:B,2,FALSE)</f>
-        <v>7526.47</v>
+        <v>4394.74</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
-        <v>10711</v>
+        <v>10510</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>738</v>
+        <v>785</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D346" s="6">
         <f>VLOOKUP(A346,Hoja1!A:B,2,FALSE)</f>
-        <v>6947.04</v>
+        <v>7414.22</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
-        <v>7225</v>
+        <v>10508</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1335</v>
+        <v>786</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D347" s="6">
         <f>VLOOKUP(A347,Hoja1!A:B,2,FALSE)</f>
-        <v>887.98</v>
+        <v>3478.58</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
-        <v>7226</v>
+        <v>10601</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1336</v>
+        <v>745</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D348" s="6">
         <f>VLOOKUP(A348,Hoja1!A:B,2,FALSE)</f>
-        <v>1002.1</v>
+        <v>3683.85</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
-        <v>11103</v>
+        <v>10609</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D349" s="6">
         <f>VLOOKUP(A349,Hoja1!A:B,2,FALSE)</f>
-        <v>4920.57</v>
+        <v>3350.15</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
-        <v>11101</v>
+        <v>10605</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D350" s="6">
         <f>VLOOKUP(A350,Hoja1!A:B,2,FALSE)</f>
-        <v>4920.57</v>
+        <v>3683.85</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
-        <v>11102</v>
+        <v>10607</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D351" s="6">
         <f>VLOOKUP(A351,Hoja1!A:B,2,FALSE)</f>
-        <v>4920.57</v>
+        <v>3683.85</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
-        <v>1003012</v>
-      </c>
-      <c r="B352" s="4"/>
+        <v>7224</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1334</v>
+      </c>
       <c r="C352" s="5" t="s">
-        <v>1441</v>
+        <v>158</v>
       </c>
       <c r="D352" s="6">
-        <v>1597.81</v>
+        <f>VLOOKUP(A352,Hoja1!A:B,2,FALSE)</f>
+        <v>2778.04</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
-        <v>1003014</v>
-      </c>
-      <c r="B353" s="4"/>
+        <v>7221</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>1331</v>
+      </c>
       <c r="C353" s="5" t="s">
-        <v>1442</v>
+        <v>159</v>
       </c>
       <c r="D353" s="6">
-        <v>1595.72</v>
+        <f>VLOOKUP(A353,Hoja1!A:B,2,FALSE)</f>
+        <v>2699.88</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
-        <v>181001</v>
-      </c>
-      <c r="B354" s="4"/>
+        <v>7227</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="C354" s="5" t="s">
-        <v>1443</v>
+        <v>160</v>
       </c>
       <c r="D354" s="6">
-        <v>1577.47</v>
+        <f>VLOOKUP(A354,Hoja1!A:B,2,FALSE)</f>
+        <v>2416.91</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
-        <v>181019</v>
-      </c>
-      <c r="B355" s="4"/>
+        <v>7223</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>1333</v>
+      </c>
       <c r="C355" s="5" t="s">
-        <v>1444</v>
+        <v>161</v>
       </c>
       <c r="D355" s="6">
-        <v>3565.76</v>
+        <f>VLOOKUP(A355,Hoja1!A:B,2,FALSE)</f>
+        <v>2276.21</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
-        <v>1801001</v>
-      </c>
-      <c r="B356" s="4"/>
+        <v>7222</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>1332</v>
+      </c>
       <c r="C356" s="5" t="s">
-        <v>1445</v>
+        <v>162</v>
       </c>
       <c r="D356" s="6">
-        <v>1700.68</v>
+        <f>VLOOKUP(A356,Hoja1!A:B,2,FALSE)</f>
+        <v>2193.36</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
-        <v>182005</v>
-      </c>
-      <c r="B357" s="4"/>
+        <v>10702</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>739</v>
+      </c>
       <c r="C357" s="5" t="s">
-        <v>1446</v>
+        <v>163</v>
       </c>
       <c r="D357" s="6">
-        <v>1587.75</v>
+        <f>VLOOKUP(A357,Hoja1!A:B,2,FALSE)</f>
+        <v>7526.47</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
-        <v>182003</v>
-      </c>
-      <c r="B358" s="4"/>
+        <v>10711</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>738</v>
+      </c>
       <c r="C358" s="5" t="s">
-        <v>1447</v>
+        <v>164</v>
       </c>
       <c r="D358" s="6">
-        <v>1464.69</v>
+        <f>VLOOKUP(A358,Hoja1!A:B,2,FALSE)</f>
+        <v>6947.04</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
-        <v>1001019</v>
-      </c>
-      <c r="B359" s="4"/>
+        <v>7225</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>1335</v>
+      </c>
       <c r="C359" s="5" t="s">
-        <v>1448</v>
+        <v>165</v>
       </c>
       <c r="D359" s="6">
-        <v>1078</v>
+        <f>VLOOKUP(A359,Hoja1!A:B,2,FALSE)</f>
+        <v>887.98</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
-        <v>1001017</v>
-      </c>
-      <c r="B360" s="4"/>
+        <v>7226</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>1336</v>
+      </c>
       <c r="C360" s="5" t="s">
-        <v>1449</v>
+        <v>166</v>
       </c>
       <c r="D360" s="6">
-        <v>648.08000000000004</v>
+        <f>VLOOKUP(A360,Hoja1!A:B,2,FALSE)</f>
+        <v>1002.1</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
-        <v>72024</v>
+        <v>11103</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1047</v>
+        <v>751</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D361" s="6">
         <f>VLOOKUP(A361,Hoja1!A:B,2,FALSE)</f>
-        <v>4684.66</v>
+        <v>4920.57</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
-        <v>72013</v>
+        <v>11101</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1001</v>
+        <v>749</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>460</v>
+        <v>168</v>
       </c>
       <c r="D362" s="6">
         <f>VLOOKUP(A362,Hoja1!A:B,2,FALSE)</f>
-        <v>31777.37</v>
+        <v>4920.57</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
-        <v>72063</v>
+        <v>11102</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1048</v>
+        <v>750</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>461</v>
+        <v>169</v>
       </c>
       <c r="D363" s="6">
         <f>VLOOKUP(A363,Hoja1!A:B,2,FALSE)</f>
-        <v>31777.37</v>
+        <v>4920.57</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
-        <v>97311</v>
-      </c>
-      <c r="B364" s="4" t="s">
-        <v>1209</v>
-      </c>
+        <v>1003012</v>
+      </c>
+      <c r="B364" s="4"/>
       <c r="C364" s="5" t="s">
-        <v>374</v>
+        <v>1441</v>
       </c>
       <c r="D364" s="6">
-        <f>VLOOKUP(A364,Hoja1!A:B,2,FALSE)</f>
-        <v>949.33</v>
+        <v>1597.81</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
-        <v>97760</v>
-      </c>
-      <c r="B365" s="4" t="s">
-        <v>1211</v>
-      </c>
+        <v>1003014</v>
+      </c>
+      <c r="B365" s="4"/>
       <c r="C365" s="5" t="s">
-        <v>375</v>
+        <v>1442</v>
       </c>
       <c r="D365" s="6">
-        <f>VLOOKUP(A365,Hoja1!A:B,2,FALSE)</f>
-        <v>797.76</v>
+        <v>1595.72</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
-        <v>97867</v>
-      </c>
-      <c r="B366" s="4" t="s">
-        <v>1208</v>
-      </c>
+        <v>181001</v>
+      </c>
+      <c r="B366" s="4"/>
       <c r="C366" s="5" t="s">
-        <v>376</v>
+        <v>1443</v>
       </c>
       <c r="D366" s="6">
-        <f>VLOOKUP(A366,Hoja1!A:B,2,FALSE)</f>
-        <v>1588.68</v>
+        <v>1577.47</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
-        <v>43961</v>
-      </c>
-      <c r="B367" s="4" t="s">
-        <v>1293</v>
-      </c>
+        <v>181019</v>
+      </c>
+      <c r="B367" s="4"/>
       <c r="C367" s="5" t="s">
-        <v>3</v>
+        <v>1444</v>
       </c>
       <c r="D367" s="6">
-        <f>VLOOKUP(A367,Hoja1!A:B,2,FALSE)</f>
-        <v>1593.56</v>
+        <v>3565.76</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
-        <v>43975</v>
-      </c>
-      <c r="B368" s="4" t="s">
-        <v>1295</v>
-      </c>
+        <v>1801001</v>
+      </c>
+      <c r="B368" s="4"/>
       <c r="C368" s="5" t="s">
-        <v>4</v>
+        <v>1445</v>
       </c>
       <c r="D368" s="6">
-        <f>VLOOKUP(A368,Hoja1!A:B,2,FALSE)</f>
-        <v>1593.56</v>
+        <v>1700.68</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
-        <v>44087</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>1297</v>
-      </c>
+        <v>182005</v>
+      </c>
+      <c r="B369" s="4"/>
       <c r="C369" s="5" t="s">
-        <v>5</v>
+        <v>1446</v>
       </c>
       <c r="D369" s="6">
-        <f>VLOOKUP(A369,Hoja1!A:B,2,FALSE)</f>
-        <v>1593.56</v>
+        <v>1587.75</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
-        <v>43962</v>
-      </c>
-      <c r="B370" s="4" t="s">
-        <v>1294</v>
-      </c>
+        <v>182003</v>
+      </c>
+      <c r="B370" s="4"/>
       <c r="C370" s="5" t="s">
-        <v>6</v>
+        <v>1447</v>
       </c>
       <c r="D370" s="6">
-        <f>VLOOKUP(A370,Hoja1!A:B,2,FALSE)</f>
-        <v>1593.56</v>
+        <v>1464.69</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
-        <v>49576</v>
-      </c>
-      <c r="B371" s="4" t="s">
-        <v>1298</v>
-      </c>
+        <v>1001019</v>
+      </c>
+      <c r="B371" s="4"/>
       <c r="C371" s="5" t="s">
-        <v>27</v>
+        <v>1448</v>
       </c>
       <c r="D371" s="6">
-        <f>VLOOKUP(A371,Hoja1!A:B,2,FALSE)</f>
-        <v>1593.56</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
-        <v>43971</v>
-      </c>
-      <c r="B372" s="4" t="s">
-        <v>1296</v>
-      </c>
+        <v>1001017</v>
+      </c>
+      <c r="B372" s="4"/>
       <c r="C372" s="5" t="s">
-        <v>7</v>
+        <v>1449</v>
       </c>
       <c r="D372" s="6">
-        <f>VLOOKUP(A372,Hoja1!A:B,2,FALSE)</f>
-        <v>1593.56</v>
+        <v>648.08000000000004</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
-        <v>586177</v>
+        <v>21332</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1299</v>
+        <v>1359</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>394</v>
+        <v>439</v>
       </c>
       <c r="D373" s="6">
         <f>VLOOKUP(A373,Hoja1!A:B,2,FALSE)</f>
-        <v>5379.66</v>
+        <v>8465.42</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="4">
-        <v>57214</v>
+        <v>21236</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1036</v>
+        <v>1352</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="D374" s="6">
         <f>VLOOKUP(A374,Hoja1!A:B,2,FALSE)</f>
-        <v>23970.18</v>
+        <v>8465.42</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
-        <v>57203</v>
+        <v>21140</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1035</v>
+        <v>1353</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="D375" s="6">
         <f>VLOOKUP(A375,Hoja1!A:B,2,FALSE)</f>
-        <v>23970.18</v>
+        <v>8465.42</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4">
-        <v>57225</v>
+        <v>21428</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1037</v>
+        <v>1357</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="D376" s="6">
         <f>VLOOKUP(A376,Hoja1!A:B,2,FALSE)</f>
-        <v>23970.18</v>
+        <v>8465.42</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
-        <v>7445</v>
+        <v>21526</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1172</v>
+        <v>1356</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>55</v>
+        <v>443</v>
       </c>
       <c r="D377" s="6">
         <f>VLOOKUP(A377,Hoja1!A:B,2,FALSE)</f>
-        <v>5597</v>
+        <v>8465.42</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
-        <v>7444</v>
+        <v>21348</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1171</v>
+        <v>1362</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>56</v>
+        <v>444</v>
       </c>
       <c r="D378" s="6">
         <f>VLOOKUP(A378,Hoja1!A:B,2,FALSE)</f>
-        <v>5597</v>
+        <v>13538.56</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
-        <v>324</v>
+        <v>21252</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1158</v>
+        <v>1363</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>36</v>
+        <v>445</v>
       </c>
       <c r="D379" s="6">
         <f>VLOOKUP(A379,Hoja1!A:B,2,FALSE)</f>
-        <v>1730</v>
+        <v>13538.56</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
-        <v>7061</v>
+        <v>21444</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1178</v>
+        <v>1367</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>57</v>
+        <v>446</v>
       </c>
       <c r="D380" s="6">
         <f>VLOOKUP(A380,Hoja1!A:B,2,FALSE)</f>
-        <v>597</v>
+        <v>13538.56</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
-        <v>7063</v>
+        <v>21542</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1179</v>
+        <v>1368</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>58</v>
+        <v>447</v>
       </c>
       <c r="D381" s="6">
         <f>VLOOKUP(A381,Hoja1!A:B,2,FALSE)</f>
-        <v>597</v>
+        <v>13538.56</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
-        <v>7069</v>
+        <v>21418</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1180</v>
+        <v>1354</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>59</v>
+        <v>448</v>
       </c>
       <c r="D382" s="6">
         <f>VLOOKUP(A382,Hoja1!A:B,2,FALSE)</f>
-        <v>1164</v>
+        <v>5811.62</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
-        <v>7059</v>
+        <v>21517</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1176</v>
+        <v>1355</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>60</v>
+        <v>449</v>
       </c>
       <c r="D383" s="6">
         <f>VLOOKUP(A383,Hoja1!A:B,2,FALSE)</f>
-        <v>597</v>
+        <v>5811.62</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
-        <v>7060</v>
+        <v>21320</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1177</v>
+        <v>1365</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>61</v>
+        <v>450</v>
       </c>
       <c r="D384" s="6">
         <f>VLOOKUP(A384,Hoja1!A:B,2,FALSE)</f>
-        <v>597</v>
+        <v>5811.62</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
-        <v>7049</v>
+        <v>21224</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1173</v>
+        <v>1364</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>62</v>
+        <v>451</v>
       </c>
       <c r="D385" s="6">
         <f>VLOOKUP(A385,Hoja1!A:B,2,FALSE)</f>
-        <v>713</v>
+        <v>5811.62</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
-        <v>7052</v>
+        <v>21124</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1175</v>
+        <v>1366</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>63</v>
+        <v>452</v>
       </c>
       <c r="D386" s="6">
         <f>VLOOKUP(A386,Hoja1!A:B,2,FALSE)</f>
-        <v>1451</v>
+        <v>5811.62</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
-        <v>7051</v>
+        <v>22336</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1174</v>
+        <v>1360</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>64</v>
+        <v>453</v>
       </c>
       <c r="D387" s="6">
         <f>VLOOKUP(A387,Hoja1!A:B,2,FALSE)</f>
-        <v>2597</v>
+        <v>12697.91</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
-        <v>6883</v>
+        <v>22240</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1168</v>
+        <v>1361</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>65</v>
+        <v>454</v>
       </c>
       <c r="D388" s="6">
         <f>VLOOKUP(A388,Hoja1!A:B,2,FALSE)</f>
-        <v>1375</v>
+        <v>12697.91</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
-        <v>6503</v>
+        <v>22140</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1159</v>
+        <v>1358</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>231</v>
+        <v>455</v>
       </c>
       <c r="D389" s="6">
         <f>VLOOKUP(A389,Hoja1!A:B,2,FALSE)</f>
-        <v>627</v>
+        <v>12697.91</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
-        <v>1462</v>
+        <v>22432</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1161</v>
+        <v>1351</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>292</v>
+        <v>456</v>
       </c>
       <c r="D390" s="6">
         <f>VLOOKUP(A390,Hoja1!A:B,2,FALSE)</f>
-        <v>4381</v>
+        <v>12697.91</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
-        <v>1461</v>
+        <v>22530</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1160</v>
+        <v>1350</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>293</v>
+        <v>457</v>
       </c>
       <c r="D391" s="6">
         <f>VLOOKUP(A391,Hoja1!A:B,2,FALSE)</f>
-        <v>3165</v>
+        <v>12697.91</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
-        <v>6483</v>
+        <v>70110</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1162</v>
+        <v>1067</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>232</v>
+        <v>14</v>
       </c>
       <c r="D392" s="6">
         <f>VLOOKUP(A392,Hoja1!A:B,2,FALSE)</f>
-        <v>2939.01</v>
+        <v>535.70000000000005</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
-        <v>5860</v>
+        <v>70210</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1163</v>
+        <v>1068</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="D393" s="6">
         <f>VLOOKUP(A393,Hoja1!A:B,2,FALSE)</f>
-        <v>6532</v>
+        <v>596.35</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
-        <v>6796</v>
+        <v>70510</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1167</v>
+        <v>1061</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>389</v>
+        <v>16</v>
       </c>
       <c r="D394" s="6">
         <f>VLOOKUP(A394,Hoja1!A:B,2,FALSE)</f>
-        <v>1688</v>
+        <v>687.33</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
-        <v>6516</v>
+        <v>70610</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1164</v>
+        <v>1069</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="D395" s="6">
         <f>VLOOKUP(A395,Hoja1!A:B,2,FALSE)</f>
-        <v>1040</v>
+        <v>747.97</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
-        <v>6518</v>
+        <v>72310</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1165</v>
+        <v>1072</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>391</v>
+        <v>96</v>
       </c>
       <c r="D396" s="6">
         <f>VLOOKUP(A396,Hoja1!A:B,2,FALSE)</f>
-        <v>1117</v>
+        <v>1091.6300000000001</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
-        <v>6520</v>
+        <v>72610</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1166</v>
+        <v>1075</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>392</v>
+        <v>97</v>
       </c>
       <c r="D397" s="6">
         <f>VLOOKUP(A397,Hoja1!A:B,2,FALSE)</f>
-        <v>1421</v>
+        <v>1172.49</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
-        <v>7442</v>
+        <v>73210</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1169</v>
+        <v>1078</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>511</v>
+        <v>98</v>
       </c>
       <c r="D398" s="6">
         <f>VLOOKUP(A398,Hoja1!A:B,2,FALSE)</f>
-        <v>3667</v>
+        <v>1233.1400000000001</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
-        <v>7443</v>
+        <v>72210</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1170</v>
+        <v>1071</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>512</v>
+        <v>99</v>
       </c>
       <c r="D399" s="6">
         <f>VLOOKUP(A399,Hoja1!A:B,2,FALSE)</f>
-        <v>5018</v>
+        <v>990.55</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
-        <v>2313</v>
+        <v>72510</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>965</v>
+        <v>1074</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="D400" s="6">
         <f>VLOOKUP(A400,Hoja1!A:B,2,FALSE)</f>
-        <v>4943.26</v>
+        <v>1071.42</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
-        <v>2302</v>
+        <v>73110</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>964</v>
+        <v>1077</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>465</v>
+        <v>101</v>
       </c>
       <c r="D401" s="6">
         <f>VLOOKUP(A401,Hoja1!A:B,2,FALSE)</f>
-        <v>29407.24</v>
+        <v>1152.27</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
-        <v>5614</v>
+        <v>72110</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>982</v>
+        <v>1070</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="D402" s="6">
         <f>VLOOKUP(A402,Hoja1!A:B,2,FALSE)</f>
-        <v>4570.1899999999996</v>
+        <v>990.55</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
-        <v>5603</v>
+        <v>72410</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>981</v>
+        <v>1073</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>466</v>
+        <v>103</v>
       </c>
       <c r="D403" s="6">
         <f>VLOOKUP(A403,Hoja1!A:B,2,FALSE)</f>
-        <v>27124.9</v>
+        <v>1051.2</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
-        <v>2657</v>
+        <v>73010</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>969</v>
+        <v>1076</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="D404" s="6">
         <f>VLOOKUP(A404,Hoja1!A:B,2,FALSE)</f>
-        <v>4943.26</v>
+        <v>1152.27</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
-        <v>2646</v>
+        <v>8582415</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>968</v>
+        <v>1079</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>467</v>
+        <v>280</v>
       </c>
       <c r="D405" s="6">
         <f>VLOOKUP(A405,Hoja1!A:B,2,FALSE)</f>
-        <v>29407.24</v>
+        <v>2324.7600000000002</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
-        <v>5679</v>
+        <v>858795</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>984</v>
+        <v>1083</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D406" s="6">
+        <v>281</v>
+      </c>
+      <c r="D406" s="6" t="e">
         <f>VLOOKUP(A406,Hoja1!A:B,2,FALSE)</f>
-        <v>4570.1899999999996</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
-        <v>5668</v>
+        <v>8587515</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>983</v>
+        <v>1082</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>468</v>
+        <v>282</v>
       </c>
       <c r="D407" s="6">
         <f>VLOOKUP(A407,Hoja1!A:B,2,FALSE)</f>
-        <v>27124.9</v>
+        <v>2324.7600000000002</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
-        <v>452112</v>
+        <v>8582515</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>554</v>
+        <v>283</v>
       </c>
       <c r="D408" s="6">
         <f>VLOOKUP(A408,Hoja1!A:B,2,FALSE)</f>
-        <v>1331</v>
+        <v>2324.7600000000002</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
-        <v>3034</v>
+        <v>8582815</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>971</v>
+        <v>1081</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="D409" s="6">
         <f>VLOOKUP(A409,Hoja1!A:B,2,FALSE)</f>
-        <v>4528.3900000000003</v>
+        <v>2324.7600000000002</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
-        <v>2423</v>
+        <v>855079</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>967</v>
+        <v>1058</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>188</v>
+        <v>538</v>
       </c>
       <c r="D410" s="6">
         <f>VLOOKUP(A410,Hoja1!A:B,2,FALSE)</f>
-        <v>4528.3900000000003</v>
+        <v>2163.04</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
-        <v>15425</v>
+        <v>855069</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1005</v>
+        <v>1064</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>189</v>
+        <v>539</v>
       </c>
       <c r="D411" s="6">
         <f>VLOOKUP(A411,Hoja1!A:B,2,FALSE)</f>
-        <v>4559.41</v>
+        <v>1293.78</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
-        <v>6445</v>
+        <v>855049</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>990</v>
+        <v>1057</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>190</v>
+        <v>540</v>
       </c>
       <c r="D412" s="6">
         <f>VLOOKUP(A412,Hoja1!A:B,2,FALSE)</f>
-        <v>4559.41</v>
+        <v>2163.04</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
-        <v>3023</v>
+        <v>855039</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>970</v>
+        <v>1063</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="D413" s="6">
         <f>VLOOKUP(A413,Hoja1!A:B,2,FALSE)</f>
-        <v>17627.900000000001</v>
+        <v>1293.78</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
-        <v>2412</v>
+        <v>855119</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>966</v>
+        <v>1060</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>470</v>
+        <v>542</v>
       </c>
       <c r="D414" s="6">
         <f>VLOOKUP(A414,Hoja1!A:B,2,FALSE)</f>
-        <v>21857.919999999998</v>
+        <v>2163.04</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
-        <v>15414</v>
+        <v>855109</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1004</v>
+        <v>1059</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>471</v>
+        <v>543</v>
       </c>
       <c r="D415" s="6">
         <f>VLOOKUP(A415,Hoja1!A:B,2,FALSE)</f>
-        <v>21857.919999999998</v>
+        <v>1293.78</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
-        <v>6423</v>
+        <v>855019</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>989</v>
+        <v>1056</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="D416" s="6">
         <f>VLOOKUP(A416,Hoja1!A:B,2,FALSE)</f>
-        <v>17627.900000000001</v>
+        <v>2163.04</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
-        <v>1547</v>
+        <v>855009</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1043</v>
+        <v>1062</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="D417" s="6" t="e">
+        <v>545</v>
+      </c>
+      <c r="D417" s="6">
         <f>VLOOKUP(A417,Hoja1!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>1293.78</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
-        <v>16031</v>
+        <v>855089</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>766</v>
+        <v>1065</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>109</v>
+        <v>546</v>
       </c>
       <c r="D418" s="6">
         <f>VLOOKUP(A418,Hoja1!A:B,2,FALSE)</f>
-        <v>5414.04</v>
+        <v>1293.78</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
-        <v>16033</v>
+        <v>855099</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>768</v>
+        <v>1066</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>110</v>
+        <v>546</v>
       </c>
       <c r="D419" s="6">
         <f>VLOOKUP(A419,Hoja1!A:B,2,FALSE)</f>
-        <v>5414.04</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A420" s="4">
-        <v>16032</v>
-      </c>
-      <c r="B420" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="C420" s="5" t="s">
-        <v>111</v>
+        <v>2163.04</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A420" s="7">
+        <v>85855</v>
+      </c>
+      <c r="B420" s="3"/>
+      <c r="C420" s="8" t="s">
+        <v>1417</v>
       </c>
       <c r="D420" s="6">
         <f>VLOOKUP(A420,Hoja1!A:B,2,FALSE)</f>
-        <v>5414.04</v>
-      </c>
-    </row>
-    <row r="421" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A421" s="4">
-        <v>16121</v>
-      </c>
-      <c r="B421" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="C421" s="5" t="s">
-        <v>221</v>
+        <v>7474.62</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A421" s="7">
+        <v>85854</v>
+      </c>
+      <c r="B421" s="3"/>
+      <c r="C421" s="8" t="s">
+        <v>1418</v>
       </c>
       <c r="D421" s="6">
         <f>VLOOKUP(A421,Hoja1!A:B,2,FALSE)</f>
-        <v>5644.6</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="4">
-        <v>16151</v>
-      </c>
-      <c r="B422" s="4" t="s">
-        <v>789</v>
-      </c>
-      <c r="C422" s="5" t="s">
-        <v>112</v>
+        <v>7474.62</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A422" s="7">
+        <v>85869</v>
+      </c>
+      <c r="B422" s="3"/>
+      <c r="C422" s="8" t="s">
+        <v>1419</v>
       </c>
       <c r="D422" s="6">
         <f>VLOOKUP(A422,Hoja1!A:B,2,FALSE)</f>
-        <v>6802.44</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A423" s="4">
-        <v>16111</v>
-      </c>
-      <c r="B423" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="C423" s="5" t="s">
-        <v>113</v>
+        <v>7474.62</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A423" s="7">
+        <v>8584712</v>
+      </c>
+      <c r="B423" s="3"/>
+      <c r="C423" s="8" t="s">
+        <v>1420</v>
       </c>
       <c r="D423" s="6">
         <f>VLOOKUP(A423,Hoja1!A:B,2,FALSE)</f>
-        <v>7961.29</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A424" s="4">
-        <v>16113</v>
-      </c>
-      <c r="B424" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C424" s="5" t="s">
-        <v>114</v>
+        <v>4476.78</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A424" s="7">
+        <v>8584812</v>
+      </c>
+      <c r="B424" s="3"/>
+      <c r="C424" s="8" t="s">
+        <v>1421</v>
       </c>
       <c r="D424" s="6">
         <f>VLOOKUP(A424,Hoja1!A:B,2,FALSE)</f>
-        <v>7961.29</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A425" s="4">
-        <v>16112</v>
-      </c>
-      <c r="B425" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="C425" s="5" t="s">
-        <v>115</v>
+        <v>4476.78</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A425" s="7">
+        <v>8580712</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="8" t="s">
+        <v>1422</v>
       </c>
       <c r="D425" s="6">
         <f>VLOOKUP(A425,Hoja1!A:B,2,FALSE)</f>
-        <v>7961.29</v>
-      </c>
-    </row>
-    <row r="426" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A426" s="4">
-        <v>550465</v>
-      </c>
-      <c r="B426" s="4" t="s">
-        <v>957</v>
-      </c>
-      <c r="C426" s="5" t="s">
-        <v>234</v>
+        <v>3751.97</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A426" s="7">
+        <v>8580312</v>
+      </c>
+      <c r="B426" s="3"/>
+      <c r="C426" s="8" t="s">
+        <v>1423</v>
       </c>
       <c r="D426" s="6">
         <f>VLOOKUP(A426,Hoja1!A:B,2,FALSE)</f>
-        <v>523.69000000000005</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A427" s="4">
-        <v>58201</v>
-      </c>
-      <c r="B427" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C427" s="5" t="s">
-        <v>474</v>
+        <v>3751.97</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A427" s="7">
+        <v>8584612</v>
+      </c>
+      <c r="B427" s="3"/>
+      <c r="C427" s="8" t="s">
+        <v>1424</v>
       </c>
       <c r="D427" s="6">
         <f>VLOOKUP(A427,Hoja1!A:B,2,FALSE)</f>
-        <v>27212.68</v>
-      </c>
-    </row>
-    <row r="428" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A428" s="4">
-        <v>19237</v>
-      </c>
-      <c r="B428" s="4" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>191</v>
+        <v>4476.78</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A428" s="7">
+        <v>85850</v>
+      </c>
+      <c r="B428" s="3"/>
+      <c r="C428" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="D428" s="6">
         <f>VLOOKUP(A428,Hoja1!A:B,2,FALSE)</f>
-        <v>4940.05</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A429" s="4">
-        <v>17465</v>
-      </c>
-      <c r="B429" s="4" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>192</v>
+        <v>1918.62</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A429" s="7">
+        <v>85849</v>
+      </c>
+      <c r="B429" s="3"/>
+      <c r="C429" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="D429" s="6">
         <f>VLOOKUP(A429,Hoja1!A:B,2,FALSE)</f>
-        <v>4940.05</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A430" s="4">
-        <v>17432</v>
-      </c>
-      <c r="B430" s="4" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C430" s="5" t="s">
-        <v>475</v>
+        <v>1918.62</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A430" s="7">
+        <v>8584512</v>
+      </c>
+      <c r="B430" s="3"/>
+      <c r="C430" s="8" t="s">
+        <v>1425</v>
       </c>
       <c r="D430" s="6">
         <f>VLOOKUP(A430,Hoja1!A:B,2,FALSE)</f>
-        <v>12684.61</v>
-      </c>
-    </row>
-    <row r="431" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A431" s="4">
-        <v>19204</v>
-      </c>
-      <c r="B431" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C431" s="5" t="s">
-        <v>476</v>
+        <v>4476.78</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A431" s="7">
+        <v>8580412</v>
+      </c>
+      <c r="B431" s="3"/>
+      <c r="C431" s="8" t="s">
+        <v>1426</v>
       </c>
       <c r="D431" s="6">
         <f>VLOOKUP(A431,Hoja1!A:B,2,FALSE)</f>
-        <v>11192.32</v>
-      </c>
-    </row>
-    <row r="432" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A432" s="4">
-        <v>4703</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>978</v>
-      </c>
-      <c r="C432" s="5" t="s">
-        <v>477</v>
+        <v>3751.97</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A432" s="7">
+        <v>8580112</v>
+      </c>
+      <c r="B432" s="3"/>
+      <c r="C432" s="8" t="s">
+        <v>1427</v>
       </c>
       <c r="D432" s="6">
         <f>VLOOKUP(A432,Hoja1!A:B,2,FALSE)</f>
-        <v>7554.8</v>
-      </c>
-    </row>
-    <row r="433" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A433" s="4">
-        <v>4747</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>979</v>
-      </c>
-      <c r="C433" s="5" t="s">
-        <v>193</v>
+        <v>3751.97</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A433" s="7">
+        <v>8580612</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="8" t="s">
+        <v>1428</v>
       </c>
       <c r="D433" s="6">
         <f>VLOOKUP(A433,Hoja1!A:B,2,FALSE)</f>
-        <v>4106.41</v>
+        <v>3751.97</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
-        <v>97361</v>
+        <v>72024</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1210</v>
+        <v>1047</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>377</v>
+        <v>182</v>
       </c>
       <c r="D434" s="6">
         <f>VLOOKUP(A434,Hoja1!A:B,2,FALSE)</f>
-        <v>1766.04</v>
+        <v>4684.66</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
-        <v>9725</v>
+        <v>72013</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1207</v>
+        <v>1001</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>378</v>
+        <v>460</v>
       </c>
       <c r="D435" s="6">
         <f>VLOOKUP(A435,Hoja1!A:B,2,FALSE)</f>
-        <v>1682.13</v>
+        <v>31777.37</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="4">
-        <v>841022</v>
+        <v>72063</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1125</v>
+        <v>1048</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>24</v>
+        <v>461</v>
       </c>
       <c r="D436" s="6">
         <f>VLOOKUP(A436,Hoja1!A:B,2,FALSE)</f>
-        <v>3307.59</v>
+        <v>31777.37</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
-        <v>841020</v>
+        <v>97311</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1126</v>
+        <v>1209</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>423</v>
+        <v>374</v>
       </c>
       <c r="D437" s="6">
         <f>VLOOKUP(A437,Hoja1!A:B,2,FALSE)</f>
-        <v>3142.58</v>
+        <v>949.33</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
-        <v>841027</v>
+        <v>97760</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1135</v>
+        <v>1211</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>424</v>
+        <v>375</v>
       </c>
       <c r="D438" s="6">
         <f>VLOOKUP(A438,Hoja1!A:B,2,FALSE)</f>
-        <v>3142.58</v>
+        <v>797.76</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
-        <v>1022005</v>
+        <v>97867</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1086</v>
+        <v>1208</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>52</v>
+        <v>376</v>
       </c>
       <c r="D439" s="6">
         <f>VLOOKUP(A439,Hoja1!A:B,2,FALSE)</f>
-        <v>3850.22</v>
+        <v>1588.68</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="4">
-        <v>1022004</v>
+        <v>43961</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1085</v>
+        <v>1293</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="D440" s="6">
         <f>VLOOKUP(A440,Hoja1!A:B,2,FALSE)</f>
-        <v>3850.22</v>
+        <v>1593.56</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
-        <v>1022001</v>
+        <v>43975</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1084</v>
+        <v>1295</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="D441" s="6">
         <f>VLOOKUP(A441,Hoja1!A:B,2,FALSE)</f>
-        <v>3516.26</v>
+        <v>1593.56</v>
       </c>
     </row>
     <row r="442" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="4">
-        <v>26633</v>
+        <v>44087</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1327</v>
+        <v>1297</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D442" s="6">
         <f>VLOOKUP(A442,Hoja1!A:B,2,FALSE)</f>
-        <v>5893.03</v>
+        <v>1593.56</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
-        <v>70110</v>
+        <v>43962</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1067</v>
+        <v>1294</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D443" s="6">
         <f>VLOOKUP(A443,Hoja1!A:B,2,FALSE)</f>
-        <v>535.70000000000005</v>
+        <v>1593.56</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="4">
-        <v>70210</v>
+        <v>49576</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1068</v>
+        <v>1298</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D444" s="6">
         <f>VLOOKUP(A444,Hoja1!A:B,2,FALSE)</f>
-        <v>596.35</v>
+        <v>1593.56</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
-        <v>70510</v>
+        <v>43971</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1061</v>
+        <v>1296</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D445" s="6">
         <f>VLOOKUP(A445,Hoja1!A:B,2,FALSE)</f>
-        <v>687.33</v>
+        <v>1593.56</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="4">
-        <v>70610</v>
+        <v>586177</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1069</v>
+        <v>1299</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>17</v>
+        <v>394</v>
       </c>
       <c r="D446" s="6">
         <f>VLOOKUP(A446,Hoja1!A:B,2,FALSE)</f>
-        <v>747.97</v>
+        <v>5379.66</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
-        <v>72310</v>
+        <v>57214</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1072</v>
+        <v>1036</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>96</v>
+        <v>462</v>
       </c>
       <c r="D447" s="6">
         <f>VLOOKUP(A447,Hoja1!A:B,2,FALSE)</f>
-        <v>1091.6300000000001</v>
+        <v>23970.18</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
-        <v>72610</v>
+        <v>57203</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1075</v>
+        <v>1035</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>97</v>
+        <v>463</v>
       </c>
       <c r="D448" s="6">
         <f>VLOOKUP(A448,Hoja1!A:B,2,FALSE)</f>
-        <v>1172.49</v>
+        <v>23970.18</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
-        <v>73210</v>
+        <v>57225</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1078</v>
+        <v>1037</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>98</v>
+        <v>464</v>
       </c>
       <c r="D449" s="6">
         <f>VLOOKUP(A449,Hoja1!A:B,2,FALSE)</f>
-        <v>1233.1400000000001</v>
+        <v>23970.18</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="4">
-        <v>72210</v>
+        <v>7445</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1071</v>
+        <v>1172</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D450" s="6">
         <f>VLOOKUP(A450,Hoja1!A:B,2,FALSE)</f>
-        <v>990.55</v>
+        <v>5597</v>
       </c>
     </row>
     <row r="451" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
-        <v>72510</v>
+        <v>7444</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1074</v>
+        <v>1171</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="D451" s="6">
         <f>VLOOKUP(A451,Hoja1!A:B,2,FALSE)</f>
-        <v>1071.42</v>
+        <v>5597</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="4">
-        <v>73110</v>
+        <v>324</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1077</v>
+        <v>1158</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="D452" s="6">
         <f>VLOOKUP(A452,Hoja1!A:B,2,FALSE)</f>
-        <v>1152.27</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="453" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
-        <v>72110</v>
+        <v>7061</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1070</v>
+        <v>1178</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D453" s="6">
         <f>VLOOKUP(A453,Hoja1!A:B,2,FALSE)</f>
-        <v>990.55</v>
+        <v>597</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="4">
-        <v>72410</v>
+        <v>7063</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1073</v>
+        <v>1179</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D454" s="6">
         <f>VLOOKUP(A454,Hoja1!A:B,2,FALSE)</f>
-        <v>1051.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="455" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
-        <v>73010</v>
+        <v>7069</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1076</v>
+        <v>1180</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="D455" s="6">
         <f>VLOOKUP(A455,Hoja1!A:B,2,FALSE)</f>
-        <v>1152.27</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="456" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
-        <v>8582415</v>
+        <v>7059</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1079</v>
+        <v>1176</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="D456" s="6">
         <f>VLOOKUP(A456,Hoja1!A:B,2,FALSE)</f>
-        <v>2324.7600000000002</v>
+        <v>597</v>
       </c>
     </row>
     <row r="457" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
-        <v>858795</v>
+        <v>7060</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1083</v>
+        <v>1177</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D457" s="6" t="e">
+        <v>61</v>
+      </c>
+      <c r="D457" s="6">
         <f>VLOOKUP(A457,Hoja1!A:B,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>597</v>
       </c>
     </row>
     <row r="458" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="4">
-        <v>8587515</v>
+        <v>7049</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1082</v>
+        <v>1173</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>282</v>
+        <v>62</v>
       </c>
       <c r="D458" s="6">
         <f>VLOOKUP(A458,Hoja1!A:B,2,FALSE)</f>
-        <v>2324.7600000000002</v>
+        <v>713</v>
       </c>
     </row>
     <row r="459" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="4">
-        <v>8582515</v>
+        <v>7052</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1080</v>
+        <v>1175</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>283</v>
+        <v>63</v>
       </c>
       <c r="D459" s="6">
         <f>VLOOKUP(A459,Hoja1!A:B,2,FALSE)</f>
-        <v>2324.7600000000002</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="4">
-        <v>8582815</v>
+        <v>7051</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>1081</v>
+        <v>1174</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>284</v>
+        <v>64</v>
       </c>
       <c r="D460" s="6">
         <f>VLOOKUP(A460,Hoja1!A:B,2,FALSE)</f>
-        <v>2324.7600000000002</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="461" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="4">
-        <v>855079</v>
+        <v>6883</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>1058</v>
+        <v>1168</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>538</v>
+        <v>65</v>
       </c>
       <c r="D461" s="6">
         <f>VLOOKUP(A461,Hoja1!A:B,2,FALSE)</f>
-        <v>2163.04</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="462" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="4">
-        <v>855069</v>
+        <v>6503</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>1064</v>
+        <v>1159</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>539</v>
+        <v>231</v>
       </c>
       <c r="D462" s="6">
         <f>VLOOKUP(A462,Hoja1!A:B,2,FALSE)</f>
-        <v>1293.78</v>
+        <v>627</v>
       </c>
     </row>
     <row r="463" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
-        <v>855049</v>
+        <v>1462</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>1057</v>
+        <v>1161</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>540</v>
+        <v>292</v>
       </c>
       <c r="D463" s="6">
         <f>VLOOKUP(A463,Hoja1!A:B,2,FALSE)</f>
-        <v>2163.04</v>
+        <v>4381</v>
       </c>
     </row>
     <row r="464" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
-        <v>855039</v>
+        <v>1461</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>1063</v>
+        <v>1160</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>541</v>
+        <v>293</v>
       </c>
       <c r="D464" s="6">
         <f>VLOOKUP(A464,Hoja1!A:B,2,FALSE)</f>
-        <v>1293.78</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="465" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
-        <v>855119</v>
+        <v>6483</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>1060</v>
+        <v>1162</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>542</v>
+        <v>232</v>
       </c>
       <c r="D465" s="6">
         <f>VLOOKUP(A465,Hoja1!A:B,2,FALSE)</f>
-        <v>2163.04</v>
+        <v>2939.01</v>
       </c>
     </row>
     <row r="466" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
-        <v>855109</v>
+        <v>5860</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>1059</v>
+        <v>1163</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>543</v>
+        <v>233</v>
       </c>
       <c r="D466" s="6">
         <f>VLOOKUP(A466,Hoja1!A:B,2,FALSE)</f>
-        <v>1293.78</v>
+        <v>6532</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
-        <v>855019</v>
+        <v>6796</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>1056</v>
+        <v>1167</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>544</v>
+        <v>389</v>
       </c>
       <c r="D467" s="6">
         <f>VLOOKUP(A467,Hoja1!A:B,2,FALSE)</f>
-        <v>2163.04</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="468" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
-        <v>855009</v>
+        <v>6516</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>1062</v>
+        <v>1164</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>545</v>
+        <v>390</v>
       </c>
       <c r="D468" s="6">
         <f>VLOOKUP(A468,Hoja1!A:B,2,FALSE)</f>
-        <v>1293.78</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="469" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
-        <v>855089</v>
+        <v>6518</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>1065</v>
+        <v>1165</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>546</v>
+        <v>391</v>
       </c>
       <c r="D469" s="6">
         <f>VLOOKUP(A469,Hoja1!A:B,2,FALSE)</f>
-        <v>1293.78</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="470" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
-        <v>855099</v>
+        <v>6520</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>1066</v>
+        <v>1166</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>546</v>
+        <v>392</v>
       </c>
       <c r="D470" s="6">
         <f>VLOOKUP(A470,Hoja1!A:B,2,FALSE)</f>
-        <v>2163.04</v>
-      </c>
-    </row>
-    <row r="471" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A471" s="7">
-        <v>85855</v>
-      </c>
-      <c r="B471" s="3"/>
-      <c r="C471" s="8" t="s">
-        <v>1417</v>
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A471" s="4">
+        <v>7442</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>511</v>
       </c>
       <c r="D471" s="6">
         <f>VLOOKUP(A471,Hoja1!A:B,2,FALSE)</f>
-        <v>7474.62</v>
-      </c>
-    </row>
-    <row r="472" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A472" s="7">
-        <v>85854</v>
-      </c>
-      <c r="B472" s="3"/>
-      <c r="C472" s="8" t="s">
-        <v>1418</v>
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A472" s="4">
+        <v>7443</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="D472" s="6">
         <f>VLOOKUP(A472,Hoja1!A:B,2,FALSE)</f>
-        <v>7474.62</v>
-      </c>
-    </row>
-    <row r="473" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A473" s="7">
-        <v>85869</v>
-      </c>
-      <c r="B473" s="3"/>
-      <c r="C473" s="8" t="s">
-        <v>1419</v>
+        <v>5018</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A473" s="4">
+        <v>2313</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="D473" s="6">
         <f>VLOOKUP(A473,Hoja1!A:B,2,FALSE)</f>
-        <v>7474.62</v>
-      </c>
-    </row>
-    <row r="474" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A474" s="7">
-        <v>8584712</v>
-      </c>
-      <c r="B474" s="3"/>
-      <c r="C474" s="8" t="s">
-        <v>1420</v>
+        <v>4943.26</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="4">
+        <v>2302</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C474" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="D474" s="6">
         <f>VLOOKUP(A474,Hoja1!A:B,2,FALSE)</f>
-        <v>4476.78</v>
-      </c>
-    </row>
-    <row r="475" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A475" s="7">
-        <v>8584812</v>
-      </c>
-      <c r="B475" s="3"/>
-      <c r="C475" s="8" t="s">
-        <v>1421</v>
+        <v>29407.24</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="4">
+        <v>5614</v>
+      </c>
+      <c r="B475" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="D475" s="6">
         <f>VLOOKUP(A475,Hoja1!A:B,2,FALSE)</f>
-        <v>4476.78</v>
-      </c>
-    </row>
-    <row r="476" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A476" s="7">
-        <v>8580712</v>
-      </c>
-      <c r="B476" s="3"/>
-      <c r="C476" s="8" t="s">
-        <v>1422</v>
+        <v>4570.1899999999996</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="4">
+        <v>5603</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="C476" s="5" t="s">
+        <v>466</v>
       </c>
       <c r="D476" s="6">
         <f>VLOOKUP(A476,Hoja1!A:B,2,FALSE)</f>
-        <v>3751.97</v>
-      </c>
-    </row>
-    <row r="477" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A477" s="7">
-        <v>8580312</v>
-      </c>
-      <c r="B477" s="3"/>
-      <c r="C477" s="8" t="s">
-        <v>1423</v>
+        <v>27124.9</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="4">
+        <v>2657</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="D477" s="6">
         <f>VLOOKUP(A477,Hoja1!A:B,2,FALSE)</f>
-        <v>3751.97</v>
-      </c>
-    </row>
-    <row r="478" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A478" s="7">
-        <v>8584612</v>
-      </c>
-      <c r="B478" s="3"/>
-      <c r="C478" s="8" t="s">
-        <v>1424</v>
+        <v>4943.26</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="4">
+        <v>2646</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="D478" s="6">
         <f>VLOOKUP(A478,Hoja1!A:B,2,FALSE)</f>
-        <v>4476.78</v>
-      </c>
-    </row>
-    <row r="479" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A479" s="7">
-        <v>85850</v>
-      </c>
-      <c r="B479" s="3"/>
-      <c r="C479" s="8" t="s">
-        <v>92</v>
+        <v>29407.24</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="4">
+        <v>5679</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C479" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="D479" s="6">
         <f>VLOOKUP(A479,Hoja1!A:B,2,FALSE)</f>
-        <v>1918.62</v>
-      </c>
-    </row>
-    <row r="480" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A480" s="7">
-        <v>85849</v>
-      </c>
-      <c r="B480" s="3"/>
-      <c r="C480" s="8" t="s">
-        <v>93</v>
+        <v>4570.1899999999996</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="4">
+        <v>5668</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C480" s="5" t="s">
+        <v>468</v>
       </c>
       <c r="D480" s="6">
         <f>VLOOKUP(A480,Hoja1!A:B,2,FALSE)</f>
-        <v>1918.62</v>
-      </c>
-    </row>
-    <row r="481" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A481" s="7">
-        <v>8584512</v>
-      </c>
-      <c r="B481" s="3"/>
-      <c r="C481" s="8" t="s">
-        <v>1425</v>
+        <v>27124.9</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="4">
+        <v>452112</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C481" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="D481" s="6">
         <f>VLOOKUP(A481,Hoja1!A:B,2,FALSE)</f>
-        <v>4476.78</v>
-      </c>
-    </row>
-    <row r="482" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A482" s="7">
-        <v>8580412</v>
-      </c>
-      <c r="B482" s="3"/>
-      <c r="C482" s="8" t="s">
-        <v>1426</v>
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="4">
+        <v>3034</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="C482" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="D482" s="6">
         <f>VLOOKUP(A482,Hoja1!A:B,2,FALSE)</f>
-        <v>3751.97</v>
-      </c>
-    </row>
-    <row r="483" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A483" s="7">
-        <v>8580112</v>
-      </c>
-      <c r="B483" s="3"/>
-      <c r="C483" s="8" t="s">
-        <v>1427</v>
+        <v>4528.3900000000003</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A483" s="4">
+        <v>2423</v>
+      </c>
+      <c r="B483" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="D483" s="6">
         <f>VLOOKUP(A483,Hoja1!A:B,2,FALSE)</f>
-        <v>3751.97</v>
-      </c>
-    </row>
-    <row r="484" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A484" s="7">
-        <v>8580612</v>
-      </c>
-      <c r="B484" s="3"/>
-      <c r="C484" s="8" t="s">
-        <v>1428</v>
+        <v>4528.3900000000003</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="4">
+        <v>15425</v>
+      </c>
+      <c r="B484" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="D484" s="6">
         <f>VLOOKUP(A484,Hoja1!A:B,2,FALSE)</f>
-        <v>3751.97</v>
+        <v>4559.41</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="4">
-        <v>21332</v>
+        <v>6445</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>1359</v>
+        <v>990</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>439</v>
+        <v>190</v>
       </c>
       <c r="D485" s="6">
         <f>VLOOKUP(A485,Hoja1!A:B,2,FALSE)</f>
-        <v>8465.42</v>
+        <v>4559.41</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="4">
-        <v>21236</v>
+        <v>3023</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>1352</v>
+        <v>970</v>
       </c>
       <c r="C486" s="5" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="D486" s="6">
         <f>VLOOKUP(A486,Hoja1!A:B,2,FALSE)</f>
-        <v>8465.42</v>
+        <v>17627.900000000001</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="4">
-        <v>21140</v>
+        <v>2412</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>1353</v>
+        <v>966</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="D487" s="6">
         <f>VLOOKUP(A487,Hoja1!A:B,2,FALSE)</f>
-        <v>8465.42</v>
+        <v>21857.919999999998</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="4">
-        <v>21428</v>
+        <v>15414</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>1357</v>
+        <v>1004</v>
       </c>
       <c r="C488" s="5" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="D488" s="6">
         <f>VLOOKUP(A488,Hoja1!A:B,2,FALSE)</f>
-        <v>8465.42</v>
+        <v>21857.919999999998</v>
       </c>
     </row>
     <row r="489" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="4">
-        <v>21526</v>
+        <v>6423</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>1356</v>
+        <v>989</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="D489" s="6">
         <f>VLOOKUP(A489,Hoja1!A:B,2,FALSE)</f>
-        <v>8465.42</v>
+        <v>17627.900000000001</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="4">
-        <v>21348</v>
+        <v>1547</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>1362</v>
+        <v>1043</v>
       </c>
       <c r="C490" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="D490" s="6">
+        <v>473</v>
+      </c>
+      <c r="D490" s="6" t="e">
         <f>VLOOKUP(A490,Hoja1!A:B,2,FALSE)</f>
-        <v>13538.56</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="491" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="4">
-        <v>21252</v>
+        <v>16031</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>1363</v>
+        <v>766</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>445</v>
+        <v>109</v>
       </c>
       <c r="D491" s="6">
         <f>VLOOKUP(A491,Hoja1!A:B,2,FALSE)</f>
-        <v>13538.56</v>
+        <v>5414.04</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="4">
-        <v>21444</v>
+        <v>16033</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>1367</v>
+        <v>768</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>446</v>
+        <v>110</v>
       </c>
       <c r="D492" s="6">
         <f>VLOOKUP(A492,Hoja1!A:B,2,FALSE)</f>
-        <v>13538.56</v>
+        <v>5414.04</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
-        <v>21542</v>
+        <v>16032</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>1368</v>
+        <v>767</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>447</v>
+        <v>111</v>
       </c>
       <c r="D493" s="6">
         <f>VLOOKUP(A493,Hoja1!A:B,2,FALSE)</f>
-        <v>13538.56</v>
+        <v>5414.04</v>
       </c>
     </row>
     <row r="494" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="4">
-        <v>21418</v>
+        <v>16121</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>1354</v>
+        <v>747</v>
       </c>
       <c r="C494" s="5" t="s">
-        <v>448</v>
+        <v>221</v>
       </c>
       <c r="D494" s="6">
         <f>VLOOKUP(A494,Hoja1!A:B,2,FALSE)</f>
-        <v>5811.62</v>
+        <v>5644.6</v>
       </c>
     </row>
     <row r="495" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="4">
-        <v>21517</v>
+        <v>16151</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>1355</v>
+        <v>789</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>449</v>
+        <v>112</v>
       </c>
       <c r="D495" s="6">
         <f>VLOOKUP(A495,Hoja1!A:B,2,FALSE)</f>
-        <v>5811.62</v>
+        <v>6802.44</v>
       </c>
     </row>
     <row r="496" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="4">
-        <v>21320</v>
+        <v>16111</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>1365</v>
+        <v>769</v>
       </c>
       <c r="C496" s="5" t="s">
-        <v>450</v>
+        <v>113</v>
       </c>
       <c r="D496" s="6">
         <f>VLOOKUP(A496,Hoja1!A:B,2,FALSE)</f>
-        <v>5811.62</v>
+        <v>7961.29</v>
       </c>
     </row>
     <row r="497" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="4">
-        <v>21224</v>
+        <v>16113</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>1364</v>
+        <v>771</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>451</v>
+        <v>114</v>
       </c>
       <c r="D497" s="6">
         <f>VLOOKUP(A497,Hoja1!A:B,2,FALSE)</f>
-        <v>5811.62</v>
+        <v>7961.29</v>
       </c>
     </row>
     <row r="498" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="4">
-        <v>21124</v>
+        <v>16112</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>1366</v>
+        <v>770</v>
       </c>
       <c r="C498" s="5" t="s">
-        <v>452</v>
+        <v>115</v>
       </c>
       <c r="D498" s="6">
         <f>VLOOKUP(A498,Hoja1!A:B,2,FALSE)</f>
-        <v>5811.62</v>
+        <v>7961.29</v>
       </c>
     </row>
     <row r="499" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="4">
-        <v>22336</v>
+        <v>550465</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>1360</v>
+        <v>957</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>453</v>
+        <v>234</v>
       </c>
       <c r="D499" s="6">
         <f>VLOOKUP(A499,Hoja1!A:B,2,FALSE)</f>
-        <v>12697.91</v>
+        <v>523.69000000000005</v>
       </c>
     </row>
     <row r="500" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="4">
-        <v>22240</v>
+        <v>58201</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>1361</v>
+        <v>1015</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="D500" s="6">
         <f>VLOOKUP(A500,Hoja1!A:B,2,FALSE)</f>
-        <v>12697.91</v>
+        <v>27212.68</v>
       </c>
     </row>
     <row r="501" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="4">
-        <v>22140</v>
+        <v>19237</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>1358</v>
+        <v>1017</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>455</v>
+        <v>191</v>
       </c>
       <c r="D501" s="6">
         <f>VLOOKUP(A501,Hoja1!A:B,2,FALSE)</f>
-        <v>12697.91</v>
+        <v>4940.05</v>
       </c>
     </row>
     <row r="502" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="4">
-        <v>22432</v>
+        <v>17465</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>1351</v>
+        <v>1010</v>
       </c>
       <c r="C502" s="5" t="s">
-        <v>456</v>
+        <v>192</v>
       </c>
       <c r="D502" s="6">
         <f>VLOOKUP(A502,Hoja1!A:B,2,FALSE)</f>
-        <v>12697.91</v>
+        <v>4940.05</v>
       </c>
     </row>
     <row r="503" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="4">
-        <v>22530</v>
+        <v>17432</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>1350</v>
+        <v>1009</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D503" s="6">
         <f>VLOOKUP(A503,Hoja1!A:B,2,FALSE)</f>
-        <v>12697.91</v>
+        <v>12684.61</v>
       </c>
     </row>
     <row r="504" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="4">
-        <v>232165</v>
+        <v>19204</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>1202</v>
+        <v>1016</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>379</v>
+        <v>476</v>
       </c>
       <c r="D504" s="6">
         <f>VLOOKUP(A504,Hoja1!A:B,2,FALSE)</f>
-        <v>638</v>
+        <v>11192.32</v>
       </c>
     </row>
     <row r="505" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="4">
-        <v>232167</v>
+        <v>4703</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>1203</v>
+        <v>978</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>380</v>
+        <v>477</v>
       </c>
       <c r="D505" s="6">
         <f>VLOOKUP(A505,Hoja1!A:B,2,FALSE)</f>
-        <v>638</v>
+        <v>7554.8</v>
       </c>
     </row>
     <row r="506" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="4">
-        <v>232168</v>
+        <v>4747</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>1204</v>
+        <v>979</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>381</v>
+        <v>193</v>
       </c>
       <c r="D506" s="6">
         <f>VLOOKUP(A506,Hoja1!A:B,2,FALSE)</f>
-        <v>638</v>
+        <v>4106.41</v>
       </c>
     </row>
     <row r="507" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="4">
-        <v>553898</v>
+        <v>97361</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>960</v>
+        <v>1210</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="D507" s="6">
         <f>VLOOKUP(A507,Hoja1!A:B,2,FALSE)</f>
-        <v>4020.23</v>
+        <v>1766.04</v>
       </c>
     </row>
     <row r="508" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="4">
-        <v>841049</v>
+        <v>9725</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>1141</v>
+        <v>1207</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>420</v>
+        <v>378</v>
       </c>
       <c r="D508" s="6">
         <f>VLOOKUP(A508,Hoja1!A:B,2,FALSE)</f>
-        <v>4572.04</v>
+        <v>1682.13</v>
       </c>
     </row>
     <row r="509" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="4">
-        <v>841001</v>
+        <v>841022</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="D509" s="6">
         <f>VLOOKUP(A509,Hoja1!A:B,2,FALSE)</f>
-        <v>3565.22</v>
+        <v>3307.59</v>
       </c>
     </row>
     <row r="510" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="4">
-        <v>841010</v>
+        <v>841020</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>1155</v>
+        <v>1126</v>
       </c>
       <c r="C510" s="5" t="s">
-        <v>10</v>
+        <v>423</v>
       </c>
       <c r="D510" s="6">
         <f>VLOOKUP(A510,Hoja1!A:B,2,FALSE)</f>
-        <v>3991.73</v>
+        <v>3142.58</v>
       </c>
     </row>
     <row r="511" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="4">
-        <v>841000</v>
+        <v>841027</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="D511" s="6">
         <f>VLOOKUP(A511,Hoja1!A:B,2,FALSE)</f>
-        <v>3308.79</v>
+        <v>3142.58</v>
       </c>
     </row>
     <row r="512" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="4">
-        <v>841009</v>
+        <v>1022005</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>1140</v>
+        <v>1086</v>
       </c>
       <c r="C512" s="5" t="s">
-        <v>334</v>
+        <v>52</v>
       </c>
       <c r="D512" s="6">
         <f>VLOOKUP(A512,Hoja1!A:B,2,FALSE)</f>
-        <v>3802.62</v>
+        <v>3850.22</v>
       </c>
     </row>
     <row r="513" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4">
-        <v>841032</v>
+        <v>1022004</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>1123</v>
+        <v>1085</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>335</v>
+        <v>53</v>
       </c>
       <c r="D513" s="6">
         <f>VLOOKUP(A513,Hoja1!A:B,2,FALSE)</f>
-        <v>3602.38</v>
+        <v>3850.22</v>
       </c>
     </row>
     <row r="514" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4">
-        <v>841002</v>
+        <v>1022001</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>1121</v>
+        <v>1084</v>
       </c>
       <c r="C514" s="5" t="s">
-        <v>336</v>
+        <v>54</v>
       </c>
       <c r="D514" s="6">
         <f>VLOOKUP(A514,Hoja1!A:B,2,FALSE)</f>
-        <v>3900</v>
+        <v>3516.26</v>
       </c>
     </row>
     <row r="515" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4">
-        <v>841011</v>
+        <v>26633</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>1156</v>
+        <v>1327</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>337</v>
+        <v>66</v>
       </c>
       <c r="D515" s="6">
         <f>VLOOKUP(A515,Hoja1!A:B,2,FALSE)</f>
-        <v>3656.15</v>
+        <v>5893.03</v>
       </c>
     </row>
     <row r="516" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="4">
-        <v>841003</v>
+        <v>232165</v>
       </c>
       <c r="B516" s="4" t="s">
-        <v>1124</v>
+        <v>1202</v>
       </c>
       <c r="C516" s="5" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D516" s="6">
         <f>VLOOKUP(A516,Hoja1!A:B,2,FALSE)</f>
-        <v>4523.72</v>
+        <v>638</v>
       </c>
     </row>
     <row r="517" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="4">
-        <v>841005</v>
+        <v>232167</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>1127</v>
+        <v>1203</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>548</v>
+        <v>380</v>
       </c>
       <c r="D517" s="6">
         <f>VLOOKUP(A517,Hoja1!A:B,2,FALSE)</f>
-        <v>3971.96</v>
+        <v>638</v>
       </c>
     </row>
     <row r="518" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="4">
-        <v>841004</v>
+        <v>232168</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>1128</v>
+        <v>1204</v>
       </c>
       <c r="C518" s="5" t="s">
-        <v>549</v>
+        <v>381</v>
       </c>
       <c r="D518" s="6">
         <f>VLOOKUP(A518,Hoja1!A:B,2,FALSE)</f>
-        <v>2633.24</v>
+        <v>638</v>
       </c>
     </row>
     <row r="519" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="4">
-        <v>841008</v>
+        <v>553898</v>
       </c>
       <c r="B519" s="4" t="s">
-        <v>1132</v>
+        <v>960</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>550</v>
+        <v>425</v>
       </c>
       <c r="D519" s="6">
         <f>VLOOKUP(A519,Hoja1!A:B,2,FALSE)</f>
-        <v>5255.87</v>
+        <v>4020.23</v>
       </c>
     </row>
     <row r="520" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="4">
-        <v>841007</v>
+        <v>841049</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="C520" s="5" t="s">
-        <v>551</v>
+        <v>420</v>
       </c>
       <c r="D520" s="6">
         <f>VLOOKUP(A520,Hoja1!A:B,2,FALSE)</f>
-        <v>3527.62</v>
+        <v>4572.04</v>
       </c>
     </row>
     <row r="521" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="4">
-        <v>841072</v>
+        <v>841001</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>1145</v>
+        <v>1122</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D521" s="6">
         <f>VLOOKUP(A521,Hoja1!A:B,2,FALSE)</f>
-        <v>3524.52</v>
+        <v>3565.22</v>
       </c>
     </row>
     <row r="522" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="4">
-        <v>841023</v>
+        <v>841010</v>
       </c>
       <c r="B522" s="4" t="s">
-        <v>1130</v>
+        <v>1155</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>602</v>
+        <v>10</v>
       </c>
       <c r="D522" s="6">
         <f>VLOOKUP(A522,Hoja1!A:B,2,FALSE)</f>
-        <v>5000.03</v>
+        <v>3991.73</v>
       </c>
     </row>
     <row r="523" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="4">
-        <v>841024</v>
+        <v>841000</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>603</v>
+        <v>333</v>
       </c>
       <c r="D523" s="6">
         <f>VLOOKUP(A523,Hoja1!A:B,2,FALSE)</f>
-        <v>5000.03</v>
+        <v>3308.79</v>
       </c>
     </row>
     <row r="524" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="4">
-        <v>6644</v>
+        <v>841009</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>991</v>
+        <v>1140</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="D524" s="6">
         <f>VLOOKUP(A524,Hoja1!A:B,2,FALSE)</f>
-        <v>4425.47</v>
+        <v>3802.62</v>
       </c>
     </row>
     <row r="525" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="4">
-        <v>66851</v>
+        <v>841032</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>1046</v>
+        <v>1123</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>478</v>
+        <v>335</v>
       </c>
       <c r="D525" s="6">
         <f>VLOOKUP(A525,Hoja1!A:B,2,FALSE)</f>
-        <v>10446.15</v>
+        <v>3602.38</v>
       </c>
     </row>
     <row r="526" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="4">
-        <v>451068</v>
+        <v>841002</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>1053</v>
+        <v>1121</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>458</v>
+        <v>336</v>
       </c>
       <c r="D526" s="6">
         <f>VLOOKUP(A526,Hoja1!A:B,2,FALSE)</f>
-        <v>1197.9000000000001</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="527" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="4">
-        <v>451073</v>
+        <v>841011</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>1054</v>
+        <v>1156</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>459</v>
+        <v>337</v>
       </c>
       <c r="D527" s="6">
         <f>VLOOKUP(A527,Hoja1!A:B,2,FALSE)</f>
-        <v>2541</v>
+        <v>3656.15</v>
       </c>
     </row>
     <row r="528" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="4">
-        <v>101827</v>
+        <v>841003</v>
       </c>
       <c r="B528" s="4" t="s">
-        <v>1182</v>
+        <v>1124</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="D528" s="6">
         <f>VLOOKUP(A528,Hoja1!A:B,2,FALSE)</f>
-        <v>3475</v>
+        <v>4523.72</v>
       </c>
     </row>
     <row r="529" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="4">
-        <v>232131</v>
+        <v>841005</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>1199</v>
+        <v>1127</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>368</v>
+        <v>548</v>
       </c>
       <c r="D529" s="6">
         <f>VLOOKUP(A529,Hoja1!A:B,2,FALSE)</f>
-        <v>569</v>
+        <v>3971.96</v>
       </c>
     </row>
     <row r="530" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="4">
-        <v>101725</v>
+        <v>841004</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>1181</v>
+        <v>1128</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>369</v>
+        <v>549</v>
       </c>
       <c r="D530" s="6">
         <f>VLOOKUP(A530,Hoja1!A:B,2,FALSE)</f>
-        <v>913.01</v>
+        <v>2633.24</v>
       </c>
     </row>
     <row r="531" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="4">
-        <v>101271</v>
+        <v>841008</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>1197</v>
+        <v>1132</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>370</v>
+        <v>550</v>
       </c>
       <c r="D531" s="6">
         <f>VLOOKUP(A531,Hoja1!A:B,2,FALSE)</f>
-        <v>906</v>
+        <v>5255.87</v>
       </c>
     </row>
     <row r="532" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="4">
-        <v>10795</v>
+        <v>841007</v>
       </c>
       <c r="B532" s="4" t="s">
-        <v>1198</v>
+        <v>1131</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>371</v>
+        <v>551</v>
       </c>
       <c r="D532" s="6">
         <f>VLOOKUP(A532,Hoja1!A:B,2,FALSE)</f>
-        <v>1810.99</v>
+        <v>3527.62</v>
       </c>
     </row>
     <row r="533" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="4">
-        <v>232317</v>
+        <v>841072</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>1206</v>
+        <v>1145</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="D533" s="6">
         <f>VLOOKUP(A533,Hoja1!A:B,2,FALSE)</f>
-        <v>1137</v>
+        <v>3524.52</v>
       </c>
     </row>
     <row r="534" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="4">
-        <v>232316</v>
+        <v>841023</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>1205</v>
+        <v>1130</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>373</v>
+        <v>602</v>
       </c>
       <c r="D534" s="6">
         <f>VLOOKUP(A534,Hoja1!A:B,2,FALSE)</f>
-        <v>1388</v>
+        <v>5000.03</v>
       </c>
     </row>
     <row r="535" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="4">
-        <v>101286</v>
+        <v>841024</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>1195</v>
+        <v>1129</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>395</v>
+        <v>603</v>
       </c>
       <c r="D535" s="6">
         <f>VLOOKUP(A535,Hoja1!A:B,2,FALSE)</f>
-        <v>1648</v>
+        <v>5000.03</v>
       </c>
     </row>
     <row r="536" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="4">
-        <v>101855</v>
+        <v>6644</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>1183</v>
+        <v>991</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>396</v>
+        <v>194</v>
       </c>
       <c r="D536" s="6">
         <f>VLOOKUP(A536,Hoja1!A:B,2,FALSE)</f>
-        <v>1449</v>
+        <v>4425.47</v>
       </c>
     </row>
     <row r="537" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="4">
-        <v>101859</v>
+        <v>66851</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>1186</v>
+        <v>1046</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>397</v>
+        <v>478</v>
       </c>
       <c r="D537" s="6">
         <f>VLOOKUP(A537,Hoja1!A:B,2,FALSE)</f>
-        <v>2180</v>
+        <v>10446.15</v>
       </c>
     </row>
     <row r="538" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="4">
-        <v>101285</v>
+        <v>451068</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>1196</v>
+        <v>1053</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="D538" s="6">
         <f>VLOOKUP(A538,Hoja1!A:B,2,FALSE)</f>
-        <v>1648</v>
+        <v>1197.9000000000001</v>
       </c>
     </row>
     <row r="539" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="4">
-        <v>101857</v>
+        <v>451073</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>1185</v>
+        <v>1054</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="D539" s="6">
         <f>VLOOKUP(A539,Hoja1!A:B,2,FALSE)</f>
-        <v>1449</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="540" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="4">
-        <v>101861</v>
+        <v>101827</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="C540" s="5" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="D540" s="6">
         <f>VLOOKUP(A540,Hoja1!A:B,2,FALSE)</f>
-        <v>2180</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="541" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="4">
-        <v>101284</v>
+        <v>232131</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="D541" s="6">
         <f>VLOOKUP(A541,Hoja1!A:B,2,FALSE)</f>
-        <v>1648</v>
+        <v>569</v>
       </c>
     </row>
     <row r="542" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="4">
-        <v>101856</v>
+        <v>101725</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="D542" s="6">
         <f>VLOOKUP(A542,Hoja1!A:B,2,FALSE)</f>
-        <v>1449</v>
+        <v>913.01</v>
       </c>
     </row>
     <row r="543" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="4">
-        <v>101860</v>
+        <v>101271</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
       <c r="D543" s="6">
         <f>VLOOKUP(A543,Hoja1!A:B,2,FALSE)</f>
-        <v>2180</v>
+        <v>906</v>
       </c>
     </row>
     <row r="544" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="4">
-        <v>101987</v>
+        <v>10795</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>1189</v>
+        <v>1198</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>547</v>
+        <v>371</v>
       </c>
       <c r="D544" s="6">
         <f>VLOOKUP(A544,Hoja1!A:B,2,FALSE)</f>
-        <v>1069</v>
+        <v>1810.99</v>
       </c>
     </row>
     <row r="545" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="4">
-        <v>582292</v>
+        <v>232317</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>1307</v>
+        <v>1206</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>29</v>
+        <v>372</v>
       </c>
       <c r="D545" s="6">
         <f>VLOOKUP(A545,Hoja1!A:B,2,FALSE)</f>
-        <v>1300.42</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="546" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="4">
-        <v>582308</v>
+        <v>232316</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>1308</v>
+        <v>1205</v>
       </c>
       <c r="C546" s="5" t="s">
-        <v>30</v>
+        <v>373</v>
       </c>
       <c r="D546" s="6">
         <f>VLOOKUP(A546,Hoja1!A:B,2,FALSE)</f>
-        <v>5198.6499999999996</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="547" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="4">
-        <v>3450</v>
+        <v>101286</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>1328</v>
+        <v>1195</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>67</v>
+        <v>395</v>
       </c>
       <c r="D547" s="6">
         <f>VLOOKUP(A547,Hoja1!A:B,2,FALSE)</f>
-        <v>1972.22</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="548" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="4">
-        <v>865</v>
+        <v>101855</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>1326</v>
+        <v>1183</v>
       </c>
       <c r="C548" s="5" t="s">
-        <v>634</v>
+        <v>396</v>
       </c>
       <c r="D548" s="6">
         <f>VLOOKUP(A548,Hoja1!A:B,2,FALSE)</f>
-        <v>1839.36</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="549" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="4">
-        <v>864</v>
+        <v>101859</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>1325</v>
+        <v>1186</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>635</v>
+        <v>397</v>
       </c>
       <c r="D549" s="6">
         <f>VLOOKUP(A549,Hoja1!A:B,2,FALSE)</f>
-        <v>1839.36</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="550" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="4">
-        <v>8504</v>
+        <v>101285</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>1115</v>
+        <v>1196</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>325</v>
+        <v>398</v>
       </c>
       <c r="D550" s="6">
         <f>VLOOKUP(A550,Hoja1!A:B,2,FALSE)</f>
-        <v>2463.56</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="551" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="4">
-        <v>101268</v>
+        <v>101857</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="D551" s="6">
         <f>VLOOKUP(A551,Hoja1!A:B,2,FALSE)</f>
-        <v>1505</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="552" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="4">
-        <v>102062</v>
+        <v>101861</v>
       </c>
       <c r="B552" s="4" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C552" s="5" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="D552" s="6">
         <f>VLOOKUP(A552,Hoja1!A:B,2,FALSE)</f>
-        <v>1976</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="553" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="4">
-        <v>232205</v>
+        <v>101284</v>
       </c>
       <c r="B553" s="4" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="D553" s="6">
         <f>VLOOKUP(A553,Hoja1!A:B,2,FALSE)</f>
-        <v>479.99</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="554" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="4">
-        <v>231266</v>
+        <v>101856</v>
       </c>
       <c r="B554" s="4" t="s">
-        <v>1193</v>
+        <v>1184</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="D554" s="6">
         <f>VLOOKUP(A554,Hoja1!A:B,2,FALSE)</f>
-        <v>1505</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="555" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="4">
-        <v>232162</v>
+        <v>101860</v>
       </c>
       <c r="B555" s="4" t="s">
-        <v>1201</v>
+        <v>1187</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="D555" s="6">
         <f>VLOOKUP(A555,Hoja1!A:B,2,FALSE)</f>
-        <v>2109.9699999999998</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="556" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4">
-        <v>232132</v>
+        <v>101987</v>
       </c>
       <c r="B556" s="4" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>387</v>
+        <v>547</v>
       </c>
       <c r="D556" s="6">
         <f>VLOOKUP(A556,Hoja1!A:B,2,FALSE)</f>
-        <v>1527</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="557" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="4">
-        <v>59646</v>
+        <v>582292</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>1042</v>
+        <v>1307</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>195</v>
+        <v>29</v>
       </c>
       <c r="D557" s="6">
         <f>VLOOKUP(A557,Hoja1!A:B,2,FALSE)</f>
-        <v>4943.26</v>
+        <v>1300.42</v>
       </c>
     </row>
     <row r="558" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="4">
-        <v>59635</v>
+        <v>582308</v>
       </c>
       <c r="B558" s="4" t="s">
-        <v>1041</v>
+        <v>1308</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>479</v>
+        <v>30</v>
       </c>
       <c r="D558" s="6">
         <f>VLOOKUP(A558,Hoja1!A:B,2,FALSE)</f>
-        <v>28968.32</v>
+        <v>5198.6499999999996</v>
       </c>
     </row>
     <row r="559" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="4">
-        <v>3723</v>
+        <v>3450</v>
       </c>
       <c r="B559" s="4" t="s">
-        <v>974</v>
+        <v>1328</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>196</v>
+        <v>67</v>
       </c>
       <c r="D559" s="6">
         <f>VLOOKUP(A559,Hoja1!A:B,2,FALSE)</f>
-        <v>4940.05</v>
+        <v>1972.22</v>
       </c>
     </row>
     <row r="560" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="4">
-        <v>3712</v>
+        <v>865</v>
       </c>
       <c r="B560" s="4" t="s">
-        <v>973</v>
+        <v>1326</v>
       </c>
       <c r="C560" s="5" t="s">
-        <v>480</v>
+        <v>634</v>
       </c>
       <c r="D560" s="6">
         <f>VLOOKUP(A560,Hoja1!A:B,2,FALSE)</f>
-        <v>20102.259999999998</v>
+        <v>1839.36</v>
       </c>
     </row>
     <row r="561" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="4">
-        <v>3701</v>
+        <v>864</v>
       </c>
       <c r="B561" s="4" t="s">
-        <v>972</v>
+        <v>1325</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>481</v>
+        <v>635</v>
       </c>
       <c r="D561" s="6">
         <f>VLOOKUP(A561,Hoja1!A:B,2,FALSE)</f>
-        <v>15713.12</v>
+        <v>1839.36</v>
       </c>
     </row>
     <row r="562" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="4">
-        <v>6724</v>
+        <v>8504</v>
       </c>
       <c r="B562" s="4" t="s">
-        <v>992</v>
+        <v>1115</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="D562" s="6">
         <f>VLOOKUP(A562,Hoja1!A:B,2,FALSE)</f>
-        <v>4943.26</v>
+        <v>2463.56</v>
       </c>
     </row>
     <row r="563" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="4">
-        <v>25332</v>
+        <v>101268</v>
       </c>
       <c r="B563" s="4" t="s">
-        <v>1018</v>
+        <v>1192</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>482</v>
+        <v>382</v>
       </c>
       <c r="D563" s="6">
         <f>VLOOKUP(A563,Hoja1!A:B,2,FALSE)</f>
-        <v>22823.54</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="564" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="4">
-        <v>40023</v>
+        <v>102062</v>
       </c>
       <c r="B564" s="4" t="s">
-        <v>1029</v>
+        <v>1190</v>
       </c>
       <c r="C564" s="5" t="s">
-        <v>198</v>
+        <v>383</v>
       </c>
       <c r="D564" s="6">
         <f>VLOOKUP(A564,Hoja1!A:B,2,FALSE)</f>
-        <v>4756.74</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="565" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="4">
-        <v>40012</v>
+        <v>232205</v>
       </c>
       <c r="B565" s="4" t="s">
-        <v>1028</v>
+        <v>1191</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>483</v>
+        <v>384</v>
       </c>
       <c r="D565" s="6">
         <f>VLOOKUP(A565,Hoja1!A:B,2,FALSE)</f>
-        <v>35903.18</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="566" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="4">
-        <v>40078</v>
+        <v>231266</v>
       </c>
       <c r="B566" s="4" t="s">
-        <v>1031</v>
+        <v>1193</v>
       </c>
       <c r="C566" s="5" t="s">
-        <v>199</v>
+        <v>385</v>
       </c>
       <c r="D566" s="6">
         <f>VLOOKUP(A566,Hoja1!A:B,2,FALSE)</f>
-        <v>4756.74</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="567" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="4">
-        <v>40067</v>
+        <v>232162</v>
       </c>
       <c r="B567" s="4" t="s">
-        <v>1030</v>
+        <v>1201</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>484</v>
+        <v>386</v>
       </c>
       <c r="D567" s="6">
         <f>VLOOKUP(A567,Hoja1!A:B,2,FALSE)</f>
-        <v>35903.18</v>
+        <v>2109.9699999999998</v>
       </c>
     </row>
     <row r="568" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="4">
-        <v>451230</v>
+        <v>232132</v>
       </c>
       <c r="B568" s="4" t="s">
-        <v>1051</v>
+        <v>1200</v>
       </c>
       <c r="C568" s="5" t="s">
-        <v>555</v>
+        <v>387</v>
       </c>
       <c r="D568" s="6">
         <f>VLOOKUP(A568,Hoja1!A:B,2,FALSE)</f>
-        <v>1331</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="569" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="4">
-        <v>451220</v>
+        <v>59646</v>
       </c>
       <c r="B569" s="4" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>556</v>
+        <v>195</v>
       </c>
       <c r="D569" s="6">
         <f>VLOOKUP(A569,Hoja1!A:B,2,FALSE)</f>
-        <v>1331</v>
+        <v>4943.26</v>
       </c>
     </row>
     <row r="570" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="4">
-        <v>84400</v>
+        <v>59635</v>
       </c>
       <c r="B570" s="4" t="s">
-        <v>1137</v>
+        <v>1041</v>
       </c>
       <c r="C570" s="5" t="s">
-        <v>200</v>
+        <v>479</v>
       </c>
       <c r="D570" s="6">
         <f>VLOOKUP(A570,Hoja1!A:B,2,FALSE)</f>
-        <v>3836.91</v>
+        <v>28968.32</v>
       </c>
     </row>
     <row r="571" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="4">
-        <v>84100</v>
+        <v>3723</v>
       </c>
       <c r="B571" s="4" t="s">
-        <v>1142</v>
+        <v>974</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D571" s="6">
         <f>VLOOKUP(A571,Hoja1!A:B,2,FALSE)</f>
-        <v>3719.54</v>
+        <v>4940.05</v>
       </c>
     </row>
     <row r="572" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="4">
-        <v>84101</v>
+        <v>3712</v>
       </c>
       <c r="B572" s="4" t="s">
-        <v>1143</v>
+        <v>973</v>
       </c>
       <c r="C572" s="5" t="s">
-        <v>202</v>
+        <v>480</v>
       </c>
       <c r="D572" s="6">
         <f>VLOOKUP(A572,Hoja1!A:B,2,FALSE)</f>
-        <v>3719.54</v>
+        <v>20102.259999999998</v>
       </c>
     </row>
     <row r="573" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="4">
-        <v>84102</v>
+        <v>3701</v>
       </c>
       <c r="B573" s="4" t="s">
-        <v>1144</v>
+        <v>972</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>203</v>
+        <v>481</v>
       </c>
       <c r="D573" s="6">
         <f>VLOOKUP(A573,Hoja1!A:B,2,FALSE)</f>
-        <v>3719.54</v>
+        <v>15713.12</v>
       </c>
     </row>
     <row r="574" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="4">
-        <v>84401</v>
+        <v>6724</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>1138</v>
+        <v>992</v>
       </c>
       <c r="C574" s="5" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D574" s="6">
         <f>VLOOKUP(A574,Hoja1!A:B,2,FALSE)</f>
-        <v>3836.91</v>
+        <v>4943.26</v>
       </c>
     </row>
     <row r="575" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="4">
-        <v>84277</v>
+        <v>25332</v>
       </c>
       <c r="B575" s="4" t="s">
-        <v>1157</v>
+        <v>1018</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>205</v>
+        <v>482</v>
       </c>
       <c r="D575" s="6">
         <f>VLOOKUP(A575,Hoja1!A:B,2,FALSE)</f>
-        <v>4318.58</v>
+        <v>22823.54</v>
       </c>
     </row>
     <row r="576" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="4">
-        <v>84280</v>
+        <v>40023</v>
       </c>
       <c r="B576" s="4" t="s">
-        <v>1146</v>
+        <v>1029</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D576" s="6">
         <f>VLOOKUP(A576,Hoja1!A:B,2,FALSE)</f>
-        <v>3872</v>
+        <v>4756.74</v>
       </c>
     </row>
     <row r="577" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="4">
-        <v>84405</v>
+        <v>40012</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>1139</v>
+        <v>1028</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>207</v>
+        <v>483</v>
       </c>
       <c r="D577" s="6">
         <f>VLOOKUP(A577,Hoja1!A:B,2,FALSE)</f>
-        <v>3836.91</v>
+        <v>35903.18</v>
       </c>
     </row>
     <row r="578" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="4">
-        <v>84403</v>
+        <v>40078</v>
       </c>
       <c r="B578" s="4" t="s">
-        <v>1136</v>
+        <v>1031</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D578" s="6">
         <f>VLOOKUP(A578,Hoja1!A:B,2,FALSE)</f>
-        <v>3836.91</v>
+        <v>4756.74</v>
       </c>
     </row>
     <row r="579" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="4">
-        <v>559115</v>
-      </c>
-      <c r="B579" s="4"/>
+        <v>40067</v>
+      </c>
+      <c r="B579" s="4" t="s">
+        <v>1030</v>
+      </c>
       <c r="C579" s="5" t="s">
-        <v>1432</v>
+        <v>484</v>
       </c>
       <c r="D579" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A579,Hoja1!A:B,2,FALSE)</f>
+        <v>35903.18</v>
       </c>
     </row>
     <row r="580" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="4">
-        <v>559118</v>
-      </c>
-      <c r="B580" s="4"/>
+        <v>451230</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>1051</v>
+      </c>
       <c r="C580" s="5" t="s">
-        <v>1433</v>
+        <v>555</v>
       </c>
       <c r="D580" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A580,Hoja1!A:B,2,FALSE)</f>
+        <v>1331</v>
       </c>
     </row>
     <row r="581" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="4">
-        <v>559117</v>
-      </c>
-      <c r="B581" s="4"/>
+        <v>451220</v>
+      </c>
+      <c r="B581" s="4" t="s">
+        <v>1052</v>
+      </c>
       <c r="C581" s="5" t="s">
-        <v>1434</v>
+        <v>556</v>
       </c>
       <c r="D581" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A581,Hoja1!A:B,2,FALSE)</f>
+        <v>1331</v>
       </c>
     </row>
     <row r="582" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="4">
-        <v>559123</v>
-      </c>
-      <c r="B582" s="4"/>
+        <v>84400</v>
+      </c>
+      <c r="B582" s="4" t="s">
+        <v>1137</v>
+      </c>
       <c r="C582" s="5" t="s">
-        <v>1435</v>
+        <v>200</v>
       </c>
       <c r="D582" s="6">
-        <v>82767.839999999997</v>
+        <f>VLOOKUP(A582,Hoja1!A:B,2,FALSE)</f>
+        <v>3836.91</v>
       </c>
     </row>
     <row r="583" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="4">
-        <v>559120</v>
-      </c>
-      <c r="B583" s="4"/>
+        <v>84100</v>
+      </c>
+      <c r="B583" s="4" t="s">
+        <v>1142</v>
+      </c>
       <c r="C583" s="5" t="s">
-        <v>1436</v>
+        <v>201</v>
       </c>
       <c r="D583" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A583,Hoja1!A:B,2,FALSE)</f>
+        <v>3719.54</v>
       </c>
     </row>
     <row r="584" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="4">
-        <v>559119</v>
-      </c>
-      <c r="B584" s="4"/>
+        <v>84101</v>
+      </c>
+      <c r="B584" s="4" t="s">
+        <v>1143</v>
+      </c>
       <c r="C584" s="5" t="s">
-        <v>1437</v>
+        <v>202</v>
       </c>
       <c r="D584" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A584,Hoja1!A:B,2,FALSE)</f>
+        <v>3719.54</v>
       </c>
     </row>
     <row r="585" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="4">
-        <v>559121</v>
-      </c>
-      <c r="B585" s="4"/>
+        <v>84102</v>
+      </c>
+      <c r="B585" s="4" t="s">
+        <v>1144</v>
+      </c>
       <c r="C585" s="5" t="s">
-        <v>1438</v>
+        <v>203</v>
       </c>
       <c r="D585" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A585,Hoja1!A:B,2,FALSE)</f>
+        <v>3719.54</v>
       </c>
     </row>
     <row r="586" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="4">
-        <v>559122</v>
-      </c>
-      <c r="B586" s="4"/>
+        <v>84401</v>
+      </c>
+      <c r="B586" s="4" t="s">
+        <v>1138</v>
+      </c>
       <c r="C586" s="5" t="s">
-        <v>1439</v>
+        <v>204</v>
       </c>
       <c r="D586" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A586,Hoja1!A:B,2,FALSE)</f>
+        <v>3836.91</v>
       </c>
     </row>
     <row r="587" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="4">
-        <v>559116</v>
-      </c>
-      <c r="B587" s="4"/>
+        <v>84277</v>
+      </c>
+      <c r="B587" s="4" t="s">
+        <v>1157</v>
+      </c>
       <c r="C587" s="5" t="s">
-        <v>1440</v>
+        <v>205</v>
       </c>
       <c r="D587" s="6">
-        <v>3448.66</v>
+        <f>VLOOKUP(A587,Hoja1!A:B,2,FALSE)</f>
+        <v>4318.58</v>
       </c>
     </row>
     <row r="588" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="4">
-        <v>559114</v>
+        <v>84280</v>
       </c>
       <c r="B588" s="4" t="s">
-        <v>963</v>
+        <v>1146</v>
       </c>
       <c r="C588" s="5" t="s">
-        <v>519</v>
+        <v>206</v>
       </c>
       <c r="D588" s="6">
         <f>VLOOKUP(A588,Hoja1!A:B,2,FALSE)</f>
-        <v>13310</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="589" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="4">
-        <v>559113</v>
+        <v>84405</v>
       </c>
       <c r="B589" s="4" t="s">
-        <v>961</v>
+        <v>1139</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>520</v>
+        <v>207</v>
       </c>
       <c r="D589" s="6">
         <f>VLOOKUP(A589,Hoja1!A:B,2,FALSE)</f>
-        <v>13310</v>
+        <v>3836.91</v>
       </c>
     </row>
     <row r="590" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="4">
-        <v>559107</v>
+        <v>84403</v>
       </c>
       <c r="B590" s="4" t="s">
-        <v>962</v>
+        <v>1136</v>
       </c>
       <c r="C590" s="5" t="s">
-        <v>521</v>
+        <v>208</v>
       </c>
       <c r="D590" s="6">
         <f>VLOOKUP(A590,Hoja1!A:B,2,FALSE)</f>
-        <v>13310</v>
+        <v>3836.91</v>
       </c>
     </row>
     <row r="591" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -6801,11 +6801,11 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1221321</v>
+        <v>1221323</v>
       </c>
       <c r="C9" t="str">
         <f>VLOOKUP(A9,BASE!A:C,2,FALSE)</f>
-        <v>ESFREBOM GUANTES DE COCINA "G" x12 un</v>
+        <v>ESFREBOM GUANTES DE COCINA "P" x12 un</v>
       </c>
       <c r="D9">
         <f>VLOOKUP(A9,BASE!A:C,3,FALSE)</f>
@@ -6833,11 +6833,11 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1221323</v>
+        <v>1221321</v>
       </c>
       <c r="C11" t="str">
         <f>VLOOKUP(A11,BASE!A:C,2,FALSE)</f>
-        <v>ESFREBOM GUANTES DE COCINA "P" x12 un</v>
+        <v>ESFREBOM GUANTES DE COCINA "G" x12 un</v>
       </c>
       <c r="D11">
         <f>VLOOKUP(A11,BASE!A:C,3,FALSE)</f>
